--- a/data_extactor/batch_10_fa/batch_0003_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0003_fa.xlsx
@@ -503,32 +503,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>نرم‌افزار مدیریت نگهداری کامپیوتری CMMS | سیستم کنترل توزیع‌شده DCS | نرم‌افزار زمان‌بندی کارکنان | نرم‌افزار کنترل موجودی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word</t>
+          <t>سیستم مدیریت نگهداری کامپیوتری CMMS | سیستم کنترل توزیع‌شده DCS | نرم‌افزار زمان‌بندی کارکنان | نرم‌افزار کنترل موجودی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخنوری | درک مطلب | گوش دادن فعال | نظارت | یادگیری فعال | نوشتار | ریاضیات | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | درک مطلب | گوش دادن فعال | نظارت | یادگیری فعال | نگارش | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>مکانیک | مهندسی و فناوری | تولید و فرآوری | مدیریت و اداره | پرسنل و منابع انسانی | ایمنی و امنیت عمومی | اداری | آموزش و پرورش | ریاضیات | کامپیوتر و الکترونیک | شیمی | زبان انگلیسی | طراحی | فیزیک | اقتصاد و حسابداری | ساختمان و ساخت‌وساز</t>
+          <t>مکانیک | مهندسی و فناوری | تولید و فرآوری | مدیریت و اداره | پرسنل و منابع انسانی | ایمنی و امنیت عمومی | اداری | آموزش و پرورش | ریاضیات | رایانه و الکترونیک | شیمی | زبان انگلیسی | طراحی | فیزیک | اقتصاد و حسابداری | ساختمان و ساخت‌وساز</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بیان نوشتاری | نظم‌دهی اطلاعات | دید نزدیک | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | دید دور | توانایی عددی | روانی ایده‌ها | توجه انتخابی | سرعت ادراکی | سرعت بستار | استدلال ریاضی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بیان کتبی | ترتیب‌دهی اطلاعات | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | بینایی دور | توانایی عددی | روانی ایده‌ها | توجه انتخابی | سرعت ادراکی | سرعت بستار | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>سلامت و ایمنی سایر کارکنان | ایمیل | بحث‌های رودررو با افراد و درون تیم‌ها | مکالمات تلفنی | استفاده از تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | محیط داخلی، بدون کنترل محیطی | نتایج کاری و خروجی‌های سایر کارکنان | کار با یا مشارکت در یک گروه یا تیم کاری | محیط داخلی، دارای کنترل محیطی | آزادی در تصمیم‌گیری | تماس با دیگران | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا صحیح بودن | قرار گرفتن در معرض صدا، سطوح نویز که حواس‌پرت‌کن یا ناراحت‌کننده هستند | تناوب تصمیم‌گیری | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | فشار زمانی | قرار گرفتن در معرض آلاینده‌ها | اهمیت تکرار وظایف مشابه | نامه‌ها و یادداشت‌های کتبی | قرار گرفتن در ارتفاعات | سرعت تعیین‌شده توسط سرعت تجهیزات | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | محیط بیرونی، قرار گرفتن در معرض تمام شرایط آب و هوایی | تعامل با مشتریان خارجی یا عموم مردم | نزدیکی فیزیکی | پیامد خطا | صرف زمان برای نشستن | قرار گرفتن در معرض تجهیزات خطرناک</t>
+          <t>سلامت و ایمنی سایر کارکنان | ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | محیط داخلی، بدون کنترل شرایط محیطی | پیامدهای کاری و نتایج سایر کارکنان | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | فراوانی تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی | قرار گرفتن در معرض آلاینده‌ها | اهمیت تکرار وظایف یکسان | نامه‌ها و یادداشت‌های کتبی | قرار گرفتن در معرض ارتفاعات بالا | سرعت تعیین‌شده توسط سرعت تجهیزات | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | فضای باز، در معرض تمام شرایط آب و هوایی | تعامل با مشتریان خارجی یا عموم مردم | نزدیکی فیزیکی | پیامد خطا | صرف زمان برای نشستن | قرار گرفتن در معرض تجهیزات خطرناک</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>تکنسین‌های فرآوری سوخت‌های زیستی | مدیران تولید سوخت‌های زیستی | مدیران فناوری و توسعه محصول سوخت‌های زیستی/بیودیزل | تکنسین‌های نیروگاه زیست‌توده | اپراتورهای کارخانه و سیستم‌های شیمیایی | مهندسان انرژی، به جز باد و خورشید | اپراتورهای کارخانه گاز | مدیران تولید زمین‌گرمایی | تکنسین‌های زمین‌گرمایی | تکنسین‌های نیروگاه برق‌آبی | مدیران تولید برق‌آبی | مهندسان صنایع | مدیران تولید صنعتی | اپراتورهای سیستم پمپ نفت، اپراتورهای پالایشگاه و اندازه‌گیرها | توزیع‌کنندگان و اعزام‌کنندگان برق | اپراتورهای نیروگاه | مهندسان ثابت و اپراتورهای دیگ بخار | اپراتورهای تصفیه‌خانه آب و فاضلاب | مدیران عملیات انرژی باد | تکنسین‌های خدمات توربین بادی</t>
+          <t>تکنسین‌های فرآوری سوخت‌های زیستی | مدیران تولید سوخت‌های زیستی | مدیران توسعه محصول و فناوری سوخت‌های زیستی/بیودیزل | تکنسین‌های نیروگاه زیست‌توده | اپراتورهای کارخانه و سامانه‌های شیمیایی | مهندسان انرژی، به جز باد و خورشید | اپراتورهای واحدهای گاز | مدیران تولید زمین‌گرمایی | تکنسین‌های زمین‌گرمایی | تکنسین‌های نیروگاه برق‌آبی | مدیران تولید برق‌آبی | مهندسان صنایع | مدیران تولید صنعتی | اپراتورهای سامانه پمپ نفت، اپراتورهای پالایشگاه و متصدیان اندازه‌گیری | توزیع‌کنندگان و دیسپچرهای برق | اپراتورهای نیروگاه برق | مهندسان تاسیسات و اپراتورهای دیگ بخار | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب | مدیران عملیات انرژی بادی | تکنسین‌های خدمات توربین بادی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -560,32 +560,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Apache Kafka | نرم‌افزار مدیریت نگهداری کامپیوتری CMMS | سیستم کنترل توزیع‌شده DCS | نرم‌افزار ایمیل | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft Word | Oracle Database | نرم‌افزار زمان‌بندی پرسنل | نرم‌افزار SAP | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار کنترل نظارتی و جمع‌آوری داده SCADA | VMware</t>
+          <t>Apache Kafka | سیستم مدیریت نگهداری کامپیوتری CMMS | سیستم کنترل توزیع‌شده DCS | نرم‌افزار ایمیل | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft Word | Oracle Database | نرم‌افزار زمان‌بندی پرسنل | نرم‌افزار SAP | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | VMware</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخنوری | درک مطلب | نظارت | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | نوشتار | علوم | ریاضیات</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نظارت | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | نگارش | علوم | ریاضیات</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>مکانیک | ایمنی و امنیت عمومی | مدیریت و اداره | زبان انگلیسی | مهندسی و فناوری | کامپیوتر و الکترونیک | پرسنل و منابع انسانی | آموزش و پرورش | ریاضیات | قانون و دولت | اداری | طراحی | فیزیک | تولید و فرآوری | روانشناسی</t>
+          <t>مکانیک | ایمنی و امنیت عمومی | مدیریت و اداره | زبان انگلیسی | مهندسی و فناوری | رایانه و الکترونیک | پرسنل و منابع انسانی | آموزش و پرورش | ریاضیات | قانون و دولت | اداری | طراحی | فیزیک | تولید و فرآوری | روان‌شناسی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بیان نوشتاری | سرعت ادراکی | تشخیص گفتار | وضوح گفتار | دید نزدیک | نظم‌دهی اطلاعات | روانی ایده‌ها | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | توانایی عددی | انعطاف‌پذیری بستار | تجسم | توجه انتخابی | تشخیص رنگ بصری | اشتراک زمانی | اصالت</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بیان کتبی | سرعت ادراکی | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | ترتیب‌دهی اطلاعات | روانی ایده‌ها | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | توانایی عددی | انعطاف‌پذیری بستار | تجسم | توجه انتخابی | تشخیص رنگ بصری | تقسیم توجه | اصالت</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | سلامت و ایمنی سایر کارکنان | بحث‌های رودررو با افراد و درون تیم‌ها | استفاده از تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | نتایج کاری و خروجی‌های سایر کارکنان | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | کار با یا مشارکت در یک گروه یا تیم کاری | تناوب تصمیم‌گیری | تماس با دیگران | محیط داخلی، دارای کنترل محیطی | اهمیت دقیق یا صحیح بودن | قرار گرفتن در معرض صدا، سطوح نویز که حواس‌پرت‌کن یا ناراحت‌کننده هستند | پیامد خطا | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | صرف زمان برای نشستن | تعامل با مشتریان خارجی یا عموم مردم | اهمیت تکرار وظایف مشابه | محیط داخلی، بدون کنترل محیطی | محیط بیرونی، قرار گرفتن در معرض تمام شرایط آب و هوایی</t>
+          <t>ایمیل | مکالمات تلفنی | سلامت و ایمنی سایر کارکنان | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | پیامدهای کاری و نتایج سایر کارکنان | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | کار با یا مشارکت در یک گروه کاری یا تیم | فراوانی تصمیم‌گیری | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | پیامد خطا | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | صرف زمان برای نشستن | تعامل با مشتریان خارجی یا عموم مردم | اهمیت تکرار وظایف یکسان | محیط داخلی، بدون کنترل شرایط محیطی | فضای باز، در معرض تمام شرایط آب و هوایی</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مدیران تولید سوخت‌های زیستی | مدیران فناوری و توسعه محصول سوخت‌های زیستی/بیودیزل | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه‌های زیست‌توده | مهندسان برق | مهندسان انرژی، به جز باد و خورشید | اپراتورهای کارخانه گاز | مدیران تولید زمین‌گرمایی | تکنسین‌های زمین‌گرمایی | تکنسین‌های نیروگاه برق‌آبی | مدیران تولید صنعتی | توزیع‌کنندگان و اعزام‌کنندگان برق | اپراتورهای نیروگاه | مهندسان سیستم‌های انرژی خورشیدی | اپراتورهای تصفیه‌خانه آب و فاضلاب | مهندسان آب/فاضلاب | مدیران توسعه انرژی باد | مهندسان انرژی باد | مدیران عملیات انرژی باد | تکنسین‌های خدمات توربین بادی</t>
+          <t>مدیران تولید سوخت‌های زیستی | مدیران توسعه محصول و فناوری سوخت‌های زیستی/بیودیزل | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه‌های زیست‌توده | مهندسان برق | مهندسان انرژی، به جز باد و خورشید | اپراتورهای واحدهای گاز | مدیران تولید زمین‌گرمایی | تکنسین‌های زمین‌گرمایی | تکنسین‌های نیروگاه برق‌آبی | مدیران تولید صنعتی | توزیع‌کنندگان و دیسپچرهای برق | اپراتورهای نیروگاه برق | مهندسان سیستم‌های انرژی خورشیدی | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب | مهندسان آب و فاضلاب | مدیران توسعه انرژی بادی | مهندسان انرژی بادی | مدیران عملیات انرژی بادی | تکنسین‌های خدمات توربین بادی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,27 +622,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>سخنوری | گوش دادن فعال | درک مطلب | نوشتار | نظارت | تفکر انتقادی | یادگیری فعال | ریاضیات | راهبردهای یادگیری</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | نظارت | تفکر انتقادی | یادگیری فعال | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>مدیریت و اداره | خدمات مشتری و شخصی | زبان انگلیسی | قانون و دولت | اقتصاد و حسابداری | کامپیوتر و الکترونیک | ریاضیات | اداری | پرسنل و منابع انسانی | آموزش و پرورش</t>
+          <t>مدیریت و اداره | خدمات مشتری و شخصی | زبان انگلیسی | قانون و دولت | اقتصاد و حسابداری | رایانه و الکترونیک | ریاضیات | اداری | پرسنل و منابع انسانی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شنیداری | بیان شفاهی | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | درک نوشتاری | روانی ایده‌ها | بیان نوشتاری | نظم‌دهی اطلاعات | استدلال استقرایی | حساسیت به مسئله | اصالت | توانایی عددی | توجه انتخابی | دید نزدیک | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی</t>
+          <t>درک شفاهی | بیان شفاهی | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | درک کتبی | روانی ایده‌ها | بیان کتبی | ترتیب‌دهی اطلاعات | استدلال استقرایی | حساسیت به مسئله | اصالت | توانایی عددی | توجه انتخابی | بینایی نزدیک | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های رودررو با افراد و درون تیم‌ها | تماس با دیگران | صرف زمان برای نشستن | کار با یا مشارکت در یک گروه یا تیم کاری | محیط داخلی، دارای کنترل محیطی | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا صحیح بودن | نامه‌ها و یادداشت‌های کتبی | آزادی در تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | فشار زمانی | نتایج کاری و خروجی‌های سایر کارکنان | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تناوب تصمیم‌گیری | اهمیت تکرار وظایف مشابه</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | صرف زمان برای نشستن | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | نامه‌ها و یادداشت‌های کتبی | آزادی در تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | فشار زمانی | پیامدهای کاری و نتایج سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | اهمیت تکرار وظایف یکسان</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | تحلیلگران هوش تجاری | خریداران و نمایندگان خرید، محصولات کشاورزی | سرپرستان خط اول کارکنان فروش غیرخرده‌فروشی | سرپرستان خط اول کارکنان پشتیبانی اداری و دفتری | مدیران عمومی و عملیات | مدیران تولید صنعتی | متخصصان لجستیک | تحلیلگران لجستیک | مهندسان لجستیک | تحلیلگران مدیریت | مدیران بازاریابی | کارمندان تدارکات | کارمندان تولید، برنامه‌ریزی و اعزام | نمایندگان خرید، به جز عمده‌فروشی، خرده‌فروشی و محصولات کشاورزی | مدیران فروش | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و مسافرتی | مدیران زنجیره تأمین | مدیران حمل‌ونقل، انبارداری و توزیع | خریداران عمده و خرده، به جز محصولات کشاورزی</t>
+          <t>مدیران خدمات اداری | تحلیلگران هوش تجاری | خریداران و نمایندگان خرید، محصولات کشاورزی | سرپرستان رده اول کارکنان فروش غیرخرده‌فروشی | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | مدیران عمومی و عملیات | مدیران تولید صنعتی | لجستیسین‌ها | تحلیلگران لجستیک | مهندسان لجستیک | تحلیل‌گران مدیریت | مدیران بازاریابی | کارمندان تدارکات | کارمندان تولید، برنامه‌ریزی و هماهنگی | نمایندگان خرید، به جز عمده‌فروشی، خرده‌فروشی و محصولات کشاورزی | مدیران فروش | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | مدیران زنجیره تأمین | مدیران حمل‌ونقل، انبارداری و توزیع | خریداران عمده‌فروشی و خرده‌فروشی، به جز محصولات کشاورزی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,32 +674,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3PL Central | ABOL Manifest Systems | ALK Technologies FleetSuite | ALK Technologies PC*Miler | نرم‌افزار سیستم‌های توزیع جهانی هواپیمایی GDS | Aljex Inventory | Amber Road | Argos Software ABECAS Insight FMS | Autodesk AutoCAD Civil 3D | نرم‌افزار سیستم گزارش‌دهی هزینه‌های خودکار | Bentley MicroStation | Bentley Transportation Data Manager | Cadre Technologies Accuplus Integrated Distribution Logistics System | Cadre Technologies Cadence Transportation Management System | Cadre Technologies Cadence Warehouse Management System | Catalyst International CatalystConnect | CoPilot Truck | DSA Foxware Warehouse Management | نرم‌افزار پایگاه داده | ESRI ArcLogistics | Eaton Fleet Advisor | نرم‌افزار ایمیل | FedEx Ship Manager | نرم‌افزار Fleetware | Four Soft 4S VisiLog | Four Soft 4S eLog | نرم‌افزار بهینه‌سازی زمان‌بندی خدمه حمل‌ونقل ریلی FRCOS | Geometrix | نرم‌افزار گرافیکی | Hewlett Packard HP-UX | HighJump Software Warehouse Advantage | IBM Lotus Notes | IBM Notes | نرم‌افزار IBM Power Systems | IBM i2 Transportation Manager | IMSure Solutions SHIPflex | Infor ERP Baan | Infosite Technologies DM Warehousing | Infosite Technologies Dispatch-Mate | Integrated Decision Support Corporation Expert Fuel | Integrated Decision Support Corporation Netwise Supply Chain | Integrated Decision Support Corporation Route Advice | Integrated Decision Support Corporation Swap Advice | Integrated Decision Support Match Advice | Integrated Decision Support Netwise Enterprise | Integrated Decision Support Netwise Frontline | IntelliTrack 3PL | IntelliTrack Warehouse Management System (WMS) | Intergraph GeoMedia Transportation Manager | نرم‌افزار کنترل موجودی | سیستم‌های مدیریت موجودی | Iptor Supply Chain | Labelmaster Software REG-Trieve | Logility Voyager WarehousePRO | Logisuite Enterprise | Logisuite Forwarder | MRA Technologies MRATrack Warehouse Management System | نرم‌افزار برنامه‌ریزی منابع مواد MRP | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics AX | Microsoft Dynamics GP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft Visio | Microsoft Word | NetSuite ERP | نرم‌افزار بهینه‌سازی | Oracle Business Intelligence Enterprise Edition | Oracle E-Business Suite Financials | Oracle E-Business Suite Logistics | Oracle JD Edwards EnterpriseOne | Oracle Primavera Enterprise Project Portfolio Management | QUALCOMM QTRACS | QUALCOMM ViaWeb | Quest Erwin Data Modeler | Radio Beacon WMS | RedPrairie DLx Warehouse | SAP Business Objects | SAP ERP Operations | نرم‌افزار SAP | نرم‌افزار سیستم مدیریت انبار SSA Global WMS | Scanlon Associates LogPak | نرم‌افزار زمان‌بندی | Sentai Pinpoint | Shipping Solutions | زبان پرس‌وجوی ساختاریافته SQL | Summary Systems Fleet Commander | نرم‌افزار مدیریت رویداد زنجیره تأمین | TECSYS EliteSeries | TECSYS PointForce Enterprise | TMW PowerSuite | نرم‌افزار سیستم مدیریت حمل‌ونقل TMS | Transtek Compass ERP | UPS WorldShip | USPS.com | Veritas NetBackup | سیستم مدیریت انبار WMS | نرم‌افزار WorkForce Software EmpCenter Time and Attendance</t>
+          <t>3PL Central | ABOL Manifest Systems | ALK Technologies FleetSuite | ALK Technologies PC*Miler | نرم‌افزار سیستم‌های توزیع جهانی هواپیمایی GDS | Aljex Inventory | Amber Road | Argos Software ABECAS Insight FMS | Autodesk AutoCAD Civil 3D | نرم‌افزار سیستم گزارش‌دهی هزینه‌های خودکار | Bentley MicroStation | Bentley Transportation Data Manager | Cadre Technologies Accuplus Integrated Distribution Logistics System | Cadre Technologies Cadence Transportation Management System | Cadre Technologies Cadence Warehouse Management System | Catalyst International CatalystConnect | CoPilot Truck | DSA Foxware Warehouse Management | نرم‌افزار پایگاه داده | ESRI ArcLogistics | Eaton Fleet Advisor | نرم‌افزار ایمیل | FedEx Ship Manager | نرم‌افزار Fleetware | Four Soft 4S VisiLog | Four Soft 4S eLog | نرم‌افزار بهینه‌سازی زمان‌بندی خدمه حمل‌ونقل ریلی FRCOS | Geometrix | نرم‌افزار گرافیکی | Hewlett Packard HP-UX | HighJump Software Warehouse Advantage | IBM Lotus Notes | IBM Notes | نرم‌افزار IBM Power Systems | IBM i2 Transportation Manager | IMSure Solutions SHIPflex | Infor ERP Baan | Infosite Technologies DM Warehousing | Infosite Technologies Dispatch-Mate | Integrated Decision Support Corporation Expert Fuel | Integrated Decision Support Corporation Netwise Supply Chain | Integrated Decision Support Corporation Route Advice | Integrated Decision Support Corporation Swap Advice | Integrated Decision Support Match Advice | Integrated Decision Support Netwise Enterprise | Integrated Decision Support Netwise Frontline | IntelliTrack 3PL | IntelliTrack Warehouse Management System (WMS) | Intergraph GeoMedia Transportation Manager | نرم‌افزار کنترل موجودی | سیستم‌های مدیریت موجودی | Iptor Supply Chain | Labelmaster Software REG-Trieve | Logility Voyager WarehousePRO | Logisuite Enterprise | Logisuite Forwarder | MRA Technologies MRATrack Warehouse Management System | نرم‌افزار برنامه‌ریزی منابع مواد MRP | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics AX | Microsoft Dynamics GP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft Visio | Microsoft Word | NetSuite ERP | نرم‌افزار بهینه‌سازی | Oracle Business Intelligence Enterprise Edition | Oracle E-Business Suite Financials | Oracle E-Business Suite Logistics | Oracle JD Edwards EnterpriseOne | Oracle Primavera Enterprise Project Portfolio Management | QUALCOMM QTRACS | QUALCOMM ViaWeb | Quest Erwin Data Modeler | Radio Beacon WMS | RedPrairie DLx Warehouse | SAP Business Objects | SAP ERP Operations | نرم‌افزار SAP | نرم‌افزار سیستم مدیریت انبار SSA Global WMS | Scanlon Associates LogPak | نرم‌افزار زمان‌بندی | Sentai Pinpoint | Shipping Solutions | زبان پرس‌وجوی ساختاریافته SQL | Summary Systems Fleet Commander | نرم‌افزار مدیریت رویداد زنجیره تأمین | TECSYS EliteSeries | TECSYS PointForce Enterprise | TMW PowerSuite | نرم‌افزار سیستم مدیریت حمل‌ونقل TMS | Transtek Compass ERP | UPS WorldShip | USPS.com | Veritas NetBackup | سیستم مدیریت انبار WMS | WorkForce Software EmpCenter Time and Attendance</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | نظارت | یادگیری فعال | نوشتار | سخنوری | تفکر انتقادی | راهبردهای یادگیری</t>
+          <t>درک مطلب | گوش دادن فعال | نظارت | یادگیری فعال | نگارش | سخن گفتن | تفکر انتقادی | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>حمل‌ونقل | مدیریت و اداره | خدمات مشتری و شخصی | زبان انگلیسی | ریاضیات | پرسنل و منابع انسانی | ایمنی و امنیت عمومی | اقتصاد و حسابداری | کامپیوتر و الکترونیک | تولید و فرآوری | قانون و دولت | اداری | آموزش و پرورش</t>
+          <t>حمل و نقل | مدیریت و اداره | خدمات مشتری و شخصی | زبان انگلیسی | ریاضیات | پرسنل و منابع انسانی | ایمنی و امنیت عمومی | اقتصاد و حسابداری | رایانه و الکترونیک | تولید و فرآوری | قانون و دولت | اداری | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان نوشتاری | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بیان شفاهی | نظم‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | دید نزدیک | وضوح گفتار | تشخیص گفتار | روانی ایده‌ها | اصالت | انعطاف‌پذیری بستار | دید دور</t>
+          <t>درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بیان شفاهی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | روانی ایده‌ها | اصالت | انعطاف‌پذیری بستار | بینایی دور</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های رودررو با افراد و درون تیم‌ها | تماس با دیگران | کار با یا مشارکت در یک گروه یا تیم کاری | تناوب تصمیم‌گیری | فشار زمانی | آزادی در تصمیم‌گیری | محیط داخلی، دارای کنترل محیطی | اهمیت دقیق یا صحیح بودن | نتایج کاری و خروجی‌های سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | نامه‌ها و یادداشت‌های کتبی | سلامت و ایمنی سایر کارکنان | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | تعامل با مشتریان خارجی یا عموم مردم | محیط داخلی، بدون کنترل محیطی | موقعیت‌های تعارض | صرف زمان برای نشستن</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | فراوانی تصمیم‌گیری | فشار زمانی | آزادی در تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | پیامدهای کاری و نتایج سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | نامه‌ها و یادداشت‌های کتبی | سلامت و ایمنی سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعامل با مشتریان خارجی یا عموم مردم | محیط داخلی، بدون کنترل شرایط محیطی | موقعیت‌های تعارض | صرف زمان برای نشستن</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>سرپرستان جابجایی بار هواپیما | نمایندگان بار و کالا | اعزام‌کنندگان، به جز پلیس، آتش‌نشانی و آمبولانس | مدیران تأسیسات | سرپرستان خط اول کمک‌کاران، کارگران و جابجا‌کنندگان مواد، دستی | سرپرستان خط اول اپراتورهای ماشین‌آلات جابجایی مواد و وسایل نقلیه | سرپرستان خط اول مهمانداران مسافر | حمل‌ونقل‌کنندگان بار | مدیران عمومی و عملیات | مدیران تولید صنعتی | متخصصان لجستیک | تحلیلگران لجستیک | مهندسان لجستیک | تحلیلگران مدیریت | کارمندان تولید، برنامه‌ریزی و اعزام | متخصصان مدیریت پروژه | مدیران خرید | کارمندان حمل‌ونقل، دریافت و موجودی | مدیران زنجیره تأمین | برنامه‌ریزان حمل‌ونقل</t>
+          <t>سرپرستان جابجایی بار هواپیما | نمایندگان بار و محموله | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | مدیران تسهیلات | سرپرستان خط اول کمک‌یارها، کارگران ساده و جابجا‌کنندگان دستی مواد | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط اول مهمانداران مسافری | متصدیان حمل و نقل | مدیران عمومی و عملیات | مدیران تولید صنعتی | لجستیسین‌ها | تحلیلگران لجستیک | مهندسان لجستیک | تحلیل‌گران مدیریت | کارمندان تولید، برنامه‌ریزی و هماهنگی | متخصصان مدیریت پروژه | مدیران خرید | کارمندان ارسال، دریافت و موجودی کالا | مدیران زنجیره تأمین | برنامه‌ریزان حمل‌ونقل</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,32 +731,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Adexa Supply Chain Planning | برنامه‌نویسی کاربردی پیشرفته کسب‌وکار ABAP | Aldata Warehouse Management | CDC Supply Chain | Dex Warehouse | Epicor SRM | Epicor WMS | نرم‌افزار گرافیکی | HighJump Software Supply Chain Advantage | HighJump Warehouse Advantage | IBM ILOG Inventory Analyst | IBM ILOG LogicNet Plus XE | IBS MRP | IBS Supply Chain Management | IFS Applications for Supply Chain Management | Infor Lawson Supply Chain Management | Infor SCM | سیستم‌های مدیریت موجودی | JDA Master Planning | Lawson S3 Supply Chain Management | نرم‌افزار MEDITECH | Manhattan Scale | Manhattan Supply Chain Process Platform | نرم‌افزار زمان‌بندی اصلی | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics AX | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SharePoint | Microsoft Visio | Microsoft Word | Minitab | NetSuite ERP | Oracle E-Business Suite Financials | Oracle Hyperion | Oracle Inventory | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | Oracle e-Business Suite Supply Chain Management | نرم‌افزار خرید | QAD Adaptive ERP | Red Prarie Warehouse Management | SAP APO | SAP BusinessObjects Crystal Reports | SAP SCM | نرم‌افزار مدیریت روابط تجاری و مشتری SAP | نرم‌افزار SAP | نرم‌افزار شبیه‌سازی و مدل‌سازی | زبان پرس‌وجوی ساختاریافته SQL | Swisslog WarehouseManager | سیستم مدیریت انبار WMS | i2 Collaborative Supply Execution | i2 Intelligence | i2 Supply Chain Visibility</t>
+          <t>Adexa Supply Chain Planning | برنامه‌نویسی پیشرفته برنامه‌های تجاری ABAP | Aldata Warehouse Management | CDC Supply Chain | Dex Warehouse | Epicor SRM | Epicor WMS | نرم‌افزار گرافیکی | HighJump Software Supply Chain Advantage | HighJump Warehouse Advantage | IBM ILOG Inventory Analyst | IBM ILOG LogicNet Plus XE | IBS MRP | IBS Supply Chain Management | IFS Applications for Supply Chain Management | Infor Lawson Supply Chain Management | Infor SCM | سیستم‌های مدیریت موجودی | JDA Master Planning | Lawson S3 Supply Chain Management | نرم‌افزار MEDITECH | Manhattan Scale | Manhattan Supply Chain Process Platform | نرم‌افزار زمان‌بندی اصلی | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics AX | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SharePoint | Microsoft Visio | Microsoft Word | Minitab | NetSuite ERP | Oracle E-Business Suite Financials | Oracle Hyperion | Oracle Inventory | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | Oracle e-Business Suite Supply Chain Management | نرم‌افزار خرید | QAD Adaptive ERP | Red Prarie Warehouse Management | SAP APO | SAP BusinessObjects Crystal Reports | SAP SCM | نرم‌افزار مدیریت روابط تجاری و مشتری SAP | نرم‌افزار SAP | نرم‌افزار شبیه‌سازی و مدل‌سازی | زبان پرس‌وجوی ساختاریافته SQL | Swisslog WarehouseManager | سیستم مدیریت انبار WMS | i2 Collaborative Supply Execution | i2 Intelligence | i2 Supply Chain Visibility</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>نظارت | سخنوری | گوش دادن فعال | درک مطلب | نوشتار | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
+          <t>نظارت | سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>حمل‌ونقل | مدیریت و اداره | زبان انگلیسی | اقتصاد و حسابداری | خدمات مشتری و شخصی | تولید و فرآوری | پرسنل و منابع انسانی | ریاضیات | کامپیوتر و الکترونیک | فروش و بازاریابی</t>
+          <t>حمل و نقل | مدیریت و اداره | زبان انگلیسی | اقتصاد و حسابداری | خدمات مشتری و شخصی | تولید و فرآوری | پرسنل و منابع انسانی | ریاضیات | رایانه و الکترونیک | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | بیان نوشتاری | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | نظم‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | دید نزدیک | تشخیص گفتار | اصالت | توجه انتخابی | استدلال ریاضی | روانی ایده‌ها | انعطاف‌پذیری بستار | توانایی عددی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | بینایی نزدیک | تشخیص گفتار | اصالت | توجه انتخابی | استدلال ریاضی | روانی ایده‌ها | انعطاف‌پذیری بستار | توانایی عددی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های رودررو با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه یا تیم کاری | تماس با دیگران | فشار زمانی | محیط داخلی، دارای کنترل محیطی | نتایج کاری و خروجی‌های سایر کارکنان | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | آزادی در تصمیم‌گیری | اهمیت دقیق یا صحیح بودن | سلامت و ایمنی سایر کارکنان | صرف زمان برای نشستن | موقعیت‌های تعارض | نامه‌ها و یادداشت‌های کتبی | تعامل با مشتریان خارجی یا عموم مردم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تناوب تصمیم‌گیری | سطح رقابت</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | فشار زمانی | محیط داخلی، دارای کنترل شرایط محیطی | پیامدهای کاری و نتایج سایر کارکنان | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | صرف زمان برای نشستن | موقعیت‌های تعارض | نامه‌ها و یادداشت‌های کتبی | تعامل با مشتریان خارجی یا عموم مردم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | سطح رقابت</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>خریداران و نمایندگان خرید، محصولات کشاورزی | سرپرستان خط اول اپراتورهای ماشین‌آلات جابجایی مواد و وسایل نقلیه | مدیران عمومی و عملیات | مهندسان صنایع | مدیران تولید صنعتی | متخصصان لجستیک | تحلیلگران لجستیک | مهندسان لجستیک | تحلیلگران مدیریت | مهندسان تولید | مدیران بازاریابی | کارمندان تدارکات | کارمندان تولید، برنامه‌ریزی و اعزام | متخصصان مدیریت پروژه | نمایندگان خرید، به جز عمده‌فروشی، خرده‌فروشی و محصولات کشاورزی | مدیران خرید | نمایندگان فروش، عمده‌فروشی و تولید، محصولات فنی و علمی | کارمندان حمل‌ونقل، دریافت و موجودی | مدیران حمل‌ونقل، انبارداری و توزیع | خریداران عمده و خرده، به جز محصولات کشاورزی</t>
+          <t>خریداران و نمایندگان خرید، محصولات کشاورزی | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | مدیران عمومی و عملیات | مهندسان صنایع | مدیران تولید صنعتی | لجستیسین‌ها | تحلیلگران لجستیک | مهندسان لجستیک | تحلیل‌گران مدیریت | مهندسان تولید | مدیران بازاریابی | کارمندان تدارکات | کارمندان تولید، برنامه‌ریزی و هماهنگی | متخصصان مدیریت پروژه | نمایندگان خرید، به جز عمده‌فروشی، خرده‌فروشی و محصولات کشاورزی | مدیران خرید | نمایندگان فروش، عمده‌فروشی و تولید، محصولات فنی و علمی | کارمندان ارسال، دریافت و موجودی کالا | مدیران حمل‌ونقل، انبارداری و توزیع | خریداران عمده‌فروشی و خرده‌فروشی، به جز محصولات کشاورزی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -788,12 +788,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>!Trak-it Solutions !Trak-it HR | ADP Employease | ADP HR/Benefits Solution | ADP Workforce Now | ASL HR Director | AdRelevance | Adobe Dreamweaver | Adobe Illustrator | Adobe PageMaker | Adobe Photoshop | Apex Business Software iHR | Apple iMovie | Ascentis HR | Asure Software HCM | Atlas Business Solutions Staff Files | Auxillium West HRnetSource | Blue Chip Computer Consultants HumaNET | Brainworks | نرم‌افزار تحلیل کسب‌وکار | Ceridian Dayforce enterprise HCM | Consultants in Data Processing HRnet | Datamatics V-Core HR | Deltek Costpoint | DenoSys HRiStragegy | نرم‌افزار سیستم مدیریت اسناد | تجربه در نرم‌افزار Webplanner | FSC Business Solutions Department Managers' Toolkit | Genesys PeopleComeFirst | Global Groupware Solutions Limited Smiles ERM On-Demand | HR-ease | HRMS Solutions iVantage | HarrisData Human Resources Information System HRIS | سیستم کدگذاری رویه‌های رایج مراقبت‌های بهداشتی HCPCS | سیستم اطلاعات منابع انسانی (HRIS) | نرم‌افزار مدیریت منابع انسانی HRMS | Humanic Design Human Resources Management System | IBM Notes | Intuit QuickBooks | Jenss &amp; Associates CompKeeper | Lawson Human Resource Management | LinkedIn | Microsoft Access | Microsoft Dynamics GP | Microsoft Dynamics Marketing | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SharePoint | Microsoft Visio | Microsoft Word | NOW Solutions emPath | NuView Systems NuViewHR | Nuview Systems Cort HCM | Oracle E-Business Suite | Oracle HRIS | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | OrangeHRM | PDS Vista | PSTek | PaloAlto Advertising Plan Pro | People-Trak HR Essentials | PerfectSoftware PerfectHR | Piney Creek Digital Protocol System | Quadkey HR Server | نرم‌افزار انتشار سازمانی Quark | Relex Weibull | نرم‌افزار SAP | Sage HRMS | Saigun Technologies EmpXtrack | Sentient Online MarketPrice | زبان پرس‌وجوی ساختاریافته SQL | Trigon Road Forte Leave Management | UCN inContact Workforce Management Software WFM | Ultimate Software UltiPro | Vantage Point Software HRA | نرم‌افزار مرورگر وب | نرم‌افزار Workday | e-MDs Bill | hSenid Business Solutions HRM Enterprise | iEmployee</t>
+          <t>!Trak-it Solutions !Trak-it HR | ADP Employease | ADP HR/Benefits Solution | ADP Workforce Now | ASL HR Director | AdRelevance | Adobe Dreamweaver | Adobe Illustrator | Adobe PageMaker | Adobe Photoshop | Apex Business Software iHR | Apple iMovie | Ascentis HR | Asure Software HCM | Atlas Business Solutions Staff Files | Auxillium West HRnetSource | Blue Chip Computer Consultants HumaNET | Brainworks | نرم‌افزار تحلیل کسب‌وکار | Ceridian Dayforce enterprise HCM | Consultants in Data Processing HRnet | Datamatics V-Core HR | Deltek Costpoint | DenoSys HRiStragegy | نرم‌افزار سیستم مدیریت اسناد | Experience in Software Webplanner | FSC Business Solutions Department Managers' Toolkit | Genesys PeopleComeFirst | Global Groupware Solutions Limited Smiles ERM On-Demand | HR-ease | HRMS Solutions iVantage | HarrisData Human Resources Information System HRIS | سیستم کدگذاری رویه‌های رایج مراقبت‌های بهداشتی HCPCS | سیستم اطلاعات منابع انسانی (HRIS) | نرم‌افزار مدیریت منابع انسانی HRMS | Humanic Design Human Resources Management System | IBM Notes | Intuit QuickBooks | Jenss &amp; Associates CompKeeper | Lawson Human Resource Management | LinkedIn | Microsoft Access | Microsoft Dynamics GP | Microsoft Dynamics Marketing | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SharePoint | Microsoft Visio | Microsoft Word | NOW Solutions emPath | NuView Systems NuViewHR | Nuview Systems Cort HCM | Oracle E-Business Suite | Oracle HRIS | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | OrangeHRM | PDS Vista | PSTek | PaloAlto Advertising Plan Pro | People-Trak HR Essentials | PerfectSoftware PerfectHR | Piney Creek Digital Protocol System | Quadkey HR Server | نرم‌افزار نشر سازمانی Quark | Relex Weibull | نرم‌افزار SAP | Sage HRMS | Saigun Technologies EmpXtrack | Sentient Online MarketPrice | زبان پرس‌وجوی ساختاریافته SQL | Trigon Road Forte Leave Management | UCN inContact Workforce Management Software WFM | Ultimate Software UltiPro | Vantage Point Software HRA | نرم‌افزار مرورگر وب | نرم‌افزار Workday | e-MDs Bill | hSenid Business Solutions HRM Enterprise | iEmployee</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>سخنوری | نوشتار | گوش دادن فعال | درک مطلب | تفکر انتقادی | یادگیری فعال | نظارت | راهبردهای یادگیری | ریاضیات</t>
+          <t>سخن گفتن | نگارش | گوش دادن فعال | درک مطلب | تفکر انتقادی | یادگیری فعال | نظارت | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -803,17 +803,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>بیان نوشتاری | درک شنیداری | درک نوشتاری | بیان شفاهی | وضوح گفتار | حساسیت به مسئله | تشخیص گفتار | استدلال قیاسی | دید نزدیک | استدلال استقرایی | استدلال ریاضی | روانی ایده‌ها | توانایی عددی | انعطاف‌پذیری دسته‌بندی | نظم‌دهی اطلاعات | اصالت</t>
+          <t>بیان کتبی | درک شفاهی | درک کتبی | بیان شفاهی | وضوح گفتار | حساسیت به مسئله | تشخیص گفتار | استدلال قیاسی | بینایی نزدیک | استدلال استقرایی | استدلال ریاضی | روانی ایده‌ها | توانایی عددی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | اصالت</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | صرف زمان برای نشستن | بحث‌های رودررو با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | تماس با دیگران | محیط داخلی، دارای کنترل محیطی | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه یا تیم کاری | اهمیت دقیق یا صحیح بودن | نامه‌ها و یادداشت‌های کتبی | تناوب تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت تکرار وظایف مشابه | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | فشار زمانی</t>
+          <t>ایمیل | مکالمات تلفنی | صرف زمان برای نشستن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت تکرار وظایف یکسان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | مدیران خدمات اداری | تحلیلگران بودجه | مدیران ارشد اجرایی | متخصصان جبران خدمات، مزایا و تحلیل شغل | مدیران انطباق | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | نمایندگان و افسران فرصت‌های برابر | بازرسان مالی | مدیران مالی | سرپرستان خط اول کارکنان پشتیبانی اداری و دفتری | دستیاران منابع انسانی، به جز حقوق و دستمزد و زمان‌سنجی | مدیران منابع انسانی | متخصصان منابع انسانی | متخصصان روابط کار | تحلیلگران مدیریت | مدیران خدمات پزشکی و بهداشتی | کارمندان حقوق و دستمزد و زمان‌سنجی | مدیران خدمات اجتماعی و جامعه | خزانه‌داران و کنترل‌کنندگان</t>
+          <t>حسابداران و حسابرسان | مدیران خدمات اداری | تحلیلگران بودجه | مدیران ارشد اجرایی | متخصصان جبران خدمات، مزایا و تحلیل شغل | مدیران انطباق | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | نمایندگان و افسران فرصت‌های برابر | بازرسان مالی | مدیران مالی | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت زمان | مدیران منابع انسانی | متخصصان منابع انسانی | متخصصان روابط کار | تحلیل‌گران مدیریت | مدیران خدمات پزشکی و بهداشتی | کارمندان حقوق و دستمزد و ثبت زمان | مدیران خدمات اجتماعی و جامعه | خزانه‌داران و کنترل‌کنندگان</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,32 +845,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AASoftTech Web Organization Chart | ADP Enterprise HR | ADP HR/Benefits Solution | ADP HR/Profile | ADP Pay eXpert | ADP Workforce Now | ADP ezLaborManager | AccountantsWorld Payroll Relief | AllNetic Working Time Tracker | نرم‌افزار ردیابی متقاضیان | Arrow Electronics N/Compass | Atlas Business Solutions Staff Files | Authoria Adviser | Automation Centre Personnel Tracker | Ceridian Dayforce enterprise HCM | Corel WordPerfect Office Suite | Data Management TimeClock Plus | Defense Travel System | Deltek Vision | Exact Software Macola ES Labor Performance | فیس‌بوک | Fidelity HR/Payroll | Halogen e360 | Halogen ePraisal | Harpers Payroll Services HR la Carte | سیستم اطلاعات منابع انسانی (HRIS) | نرم‌افزار مدیریت منابع انسانی HRMS | IBM Cognos Impromptu | IBM Lotus 1-2-3 | IBM Notes | IBM SPSS Statistics | Inception Technologies InfiniTime | Infor ERP SyteLine | Infor SSA Human Capital Management | Infotronics Attendance Enterprise | Intuit QuickBooks | Jantek Electronics Jupiter Time &amp; Attendance | Kronos Enterprise Workforce Management | Kronos Workforce Timekeeper | Lawson Human Resource Management | Lawson Human Resources Suite | LinkedIn | Mentimeter | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SharePoint Server | Microsoft Visio | Microsoft Word | Midrange Software XpertHire | Nearpod | New World Systems Logos.NET | Norchard Solutions Succession Wizard | Nuvosoft Rwiz | Oracle Business Intelligence Enterprise Edition | Oracle E-Business Suite Financials | Oracle Fusion Applications | Oracle HRIS | Oracle PeopleSoft | Oracle Taleo | خواننده‌های PDF | نرم‌افزار حقوق و دستمزد Paychex | مدیریت حقوق و دستمزد Paycor | Paylocity Web Pay | نرم‌افزار People-Trak | نرم‌افزار Pereless Systems | Qqest TimeForce | QuestionMark | SAP BusinessObjects Crystal Reports | نرم‌افزار SAP | Sage 50 Accounting | Sage HRMS | Savitr RecruitX | سایت‌های رسانه‌های اجتماعی | Soft Trac Microix Timesheet | سیستم استاندارد گزارش‌دهی پرسنل بخش SIDPERS | Stratitec TimeIPS | Stromberg Enterprise | Tesseract Benefits Manager | Tesseract Human Resources Manager | سیستم اطلاعات مدیریت پرسنل افسری کل TOPMIS | نرم‌افزار آموزشی | Tyler Technologies MUNIS | UCN inContact Workforce Management Software WFM | Ultimate Software UltiPro Workplace | UniFocus Watson Human Resources Manager | Unicorn HRO Open4 | نرم‌افزار مرورگر وب | WhizLabs | WinOcular | نرم‌افزار Workday | یوتیوب | iSystems Evolution Payroll and Tax Management | سیستم مدیریت الکترونیکی سوابق پرسنلی تعاملی iPERMS | peoplefluent Performance | peoplefluent Recruiting</t>
+          <t>AASoftTech Web Organization Chart | ADP Enterprise HR | ADP HR/Benefits Solution | ADP HR/Profile | ADP Pay eXpert | ADP Workforce Now | ADP ezLaborManager | AccountantsWorld Payroll Relief | AllNetic Working Time Tracker | نرم‌افزار ردیابی متقاضی | Arrow Electronics N/Compass | Atlas Business Solutions Staff Files | Authoria Adviser | Automation Centre Personnel Tracker | Ceridian Dayforce enterprise HCM | Corel WordPerfect Office Suite | Data Management TimeClock Plus | Defense Travel System | Deltek Vision | Exact Software Macola ES Labor Performance | Facebook | Fidelity HR/Payroll | Halogen e360 | Halogen ePraisal | Harpers Payroll Services HR la Carte | سیستم اطلاعات منابع انسانی (HRIS) | نرم‌افزار مدیریت منابع انسانی HRMS | IBM Cognos Impromptu | IBM Lotus 1-2-3 | IBM Notes | IBM SPSS Statistics | Inception Technologies InfiniTime | Infor ERP SyteLine | Infor SSA Human Capital Management | Infotronics Attendance Enterprise | Intuit QuickBooks | Jantek Electronics Jupiter Time &amp; Attendance | Kronos Enterprise Workforce Management | Kronos Workforce Timekeeper | Lawson Human Resource Management | Lawson Human Resources Suite | LinkedIn | Mentimeter | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SharePoint Server | Microsoft Visio | Microsoft Word | Midrange Software XpertHire | Nearpod | New World Systems Logos.NET | Norchard Solutions Succession Wizard | Nuvosoft Rwiz | Oracle Business Intelligence Enterprise Edition | Oracle E-Business Suite Financials | Oracle Fusion Applications | Oracle HRIS | Oracle PeopleSoft | Oracle Taleo | خواننده‌های PDF | نرم‌افزار حقوق و دستمزد Paychex | مدیریت حقوق و دستمزد Paycor | Paylocity Web Pay | نرم‌افزار People-Trak | نرم‌افزار Pereless Systems | Qqest TimeForce | QuestionMark | SAP BusinessObjects Crystal Reports | نرم‌افزار SAP | Sage 50 Accounting | Sage HRMS | Savitr RecruitX | سایت‌های رسانه‌های اجتماعی | Soft Trac Microix Timesheet | سیستم استاندارد گزارش‌دهی پرسنل بخش SIDPERS | Stratitec TimeIPS | Stromberg Enterprise | Tesseract Benefits Manager | Tesseract Human Resources Manager | سیستم اطلاعات مدیریت پرسنل افسری کل TOPMIS | نرم‌افزار آموزشی | Tyler Technologies MUNIS | UCN inContact Workforce Management Software WFM | Ultimate Software UltiPro Workplace | UniFocus Watson Human Resources Manager | Unicorn HRO Open4 | نرم‌افزار مرورگر وب | WhizLabs | WinOcular | نرم‌افزار Workday | YouTube | iSystems Evolution Payroll and Tax Management | سیستم مدیریت الکترونیکی سوابق پرسنلی تعاملی iPERMS | peoplefluent Performance | peoplefluent Recruiting</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخنوری | درک مطلب | نوشتار | نظارت | یادگیری فعال | تفکر انتقادی | راهبردهای یادگیری | ریاضیات</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نگارش | نظارت | یادگیری فعال | تفکر انتقادی | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>پرسنل و منابع انسانی | زبان انگلیسی | مدیریت و اداره | خدمات مشتری و شخصی | آموزش و پرورش | قانون و دولت | روانشناسی | ایمنی و امنیت عمومی | کامپیوتر و الکترونیک | ارتباطات و رسانه | ریاضیات</t>
+          <t>پرسنل و منابع انسانی | زبان انگلیسی | مدیریت و اداره | خدمات مشتری و شخصی | آموزش و پرورش | قانون و دولت | روان‌شناسی | ایمنی و امنیت عمومی | رایانه و الکترونیک | ارتباطات و رسانه | ریاضیات</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شنیداری | درک نوشتاری | بیان نوشتاری | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | دید نزدیک | تشخیص گفتار | حساسیت به مسئله | روانی ایده‌ها | اصالت | نظم‌دهی اطلاعات | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | سرعت بستار | حفظ کردن | توانایی عددی | استدلال ریاضی</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | تشخیص گفتار | حساسیت به مسئله | روانی ایده‌ها | اصالت | ترتیب‌دهی اطلاعات | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | سرعت بستار | حفظ کردن | توانایی عددی | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های رودررو با افراد و درون تیم‌ها | تماس با دیگران | کار با یا مشارکت در یک گروه یا تیم کاری | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | صرف زمان برای نشستن | تناوب تصمیم‌گیری | اهمیت دقیق یا صحیح بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | محیط داخلی، دارای کنترل محیطی | موقعیت‌های تعارض | فشار زمانی | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | نامه‌ها و یادداشت‌های کتبی | نتایج کاری و خروجی‌های سایر کارکنان | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | تعامل با مشتریان خارجی یا عموم مردم | سلامت و ایمنی سایر کارکنان</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | صرف زمان برای نشستن | فراوانی تصمیم‌گیری | اهمیت دقیق یا درست بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | محیط داخلی، دارای کنترل شرایط محیطی | موقعیت‌های تعارض | فشار زمانی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نامه‌ها و یادداشت‌های کتبی | پیامدهای کاری و نتایج سایر کارکنان | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | تعامل با مشتریان خارجی یا عموم مردم | سلامت و ایمنی سایر کارکنان</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | مدیران ارشد اجرایی | مدیران جبران خدمات و مزایا | متخصصان جبران خدمات، مزایا و تحلیل شغل | مدیران انطباق | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | نمایندگان و افسران فرصت‌های برابر | سرپرستان خط اول کارکنان پشتیبانی اداری و دفتری | دستیاران منابع انسانی، به جز حقوق و دستمزد و زمان‌سنجی | متخصصان منابع انسانی | روانشناسان صنعتی-سازمانی | متخصصان روابط کار | تحلیلگران مدیریت | مدیران خدمات پزشکی و بهداشتی | کارمندان حقوق و دستمزد و زمان‌سنجی | متخصصان مدیریت پروژه | مدیران روابط عمومی | مدیران خدمات اجتماعی و جامعه | مدیران آموزش و توسعه | متخصصان آموزش و توسعه</t>
+          <t>مدیران خدمات اداری | مدیران ارشد اجرایی | مدیران جبران خدمات و مزایا | متخصصان جبران خدمات، مزایا و تحلیل شغل | مدیران انطباق | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | نمایندگان و افسران فرصت‌های برابر | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت زمان | متخصصان منابع انسانی | روان‌شناسان صنعتی-سازمانی | متخصصان روابط کار | تحلیل‌گران مدیریت | مدیران خدمات پزشکی و بهداشتی | کارمندان حقوق و دستمزد و ثبت زمان | متخصصان مدیریت پروژه | مدیران روابط عمومی | مدیران خدمات اجتماعی و جامعه | مدیران آموزش و توسعه | متخصصان آموزش و توسعه</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>راهبردهای یادگیری | سخنوری | گوش دادن فعال | درک مطلب | نوشتار | نظارت | تفکر انتقادی | یادگیری فعال</t>
+          <t>راهبردهای یادگیری | سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | نظارت | تفکر انتقادی | یادگیری فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>آموزش و پرورش | زبان انگلیسی | مدیریت و اداره | پرسنل و منابع انسانی | خدمات مشتری و شخصی | ارتباطات و رسانه | روانشناسی | کامپیوتر و الکترونیک</t>
+          <t>آموزش و پرورش | زبان انگلیسی | مدیریت و اداره | پرسنل و منابع انسانی | خدمات مشتری و شخصی | ارتباطات و رسانه | روان‌شناسی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شنیداری | درک نوشتاری | بیان نوشتاری | روانی ایده‌ها | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | دید نزدیک | اصالت | حساسیت به مسئله | استدلال استقرایی | نظم‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | روانی ایده‌ها | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | اصالت | حساسیت به مسئله | استدلال استقرایی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>کار با یا مشارکت در یک گروه یا تیم کاری | ایمیل | بحث‌های رودررو با افراد و درون تیم‌ها | مکالمات تلفنی | تماس با دیگران | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای نشستن | محیط داخلی، دارای کنترل محیطی | آزادی در تصمیم‌گیری | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | نتایج کاری و خروجی‌های سایر کارکنان | فشار زمانی</t>
+          <t>کار با یا مشارکت در یک گروه کاری یا تیم | ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای نشستن | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامدهای کاری و نتایج سایر کارکنان | فشار زمانی</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>معلمان آموزش شغلی/فنی، دوره متوسطه | معلمان آموزش شغلی/فنی، دوره پس از متوسطه | مدیران آموزشی، مهدکودک تا متوسطه | مدیران آموزشی، دوره پس از متوسطه | معلمان آموزشی، دوره پس از متوسطه | مدیران آموزشی و مراقبت از کودک، پیش‌دبستانی و مهدکودک | مشاوران و راهنمایان آموزشی، راهنمایی و شغلی | سرپرستان خط اول کارکنان سرگرمی و تفریحی، به جز خدمات قمار | دستیاران منابع انسانی، به جز حقوق و دستمزد و زمان‌سنجی | مدیران منابع انسانی | متخصصان منابع انسانی | روانشناسان صنعتی-سازمانی | هماهنگ‌کنندگان آموزشی | تحلیلگران مدیریت | مدیران خدمات پزشکی و بهداشتی | متخصصان مدیریت پروژه | مشاوران توانبخشی | مدیران خدمات اجتماعی و جامعه | معلمان آموزش ویژه، مهدکودک | متخصصان آموزش و توسعه</t>
+          <t>معلمان آموزش‌های شغلی/فنی، دوره راهنمایی | اساتید آموزش‌های شغلی/فنی، پس از متوسطه | مدیران آموزشی، مهدکودک تا دبیرستان | مدیران آموزشی، پس از متوسطه | مدرسان علوم تربیتی، آموزش عالی | مدیران آموزش و مراقبت از کودکان، پیش‌دبستانی و مهدکودک | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | سرپرستان خط اول کارگران سرگرمی و تفریح، به جز خدمات قمار | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت زمان | مدیران منابع انسانی | متخصصان منابع انسانی | روان‌شناسان صنعتی-سازمانی | هماهنگ‌کنندگان آموزشی | تحلیل‌گران مدیریت | مدیران خدمات پزشکی و بهداشتی | متخصصان مدیریت پروژه | مشاوران توانبخشی | مدیران خدمات اجتماعی و جامعه | معلمان آموزش ویژه، کودکستان | متخصصان آموزش و توسعه</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -959,12 +959,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>AGCO Advanced Technology Solutions Fieldstar | Accutech Systems Corporation AccuFarm-MGR | Adobe Photoshop | Advanced Veterinary Services Ranch Vision | Ag Connections Land.db | Ag Leader Technology SMS Advanced | AgData Blue Skies Accounting | AgTerra Technologies AgTrac | Agevo Farm Manager | AgriSoft/CMC AgriSoft/ERP | Alua Software Paddock Pro | AquaSoft Farm Manager | Argos Software ABECAS Insight | Atlassian Confluence | Brihzon Solutions SMART Dairy Resource Planning | CDA International Manifold System | CattleWorks | Cattlesoft CattleMax | Countryside Data Ag Payroll | Custom Software Group CSG AgroSys | DIVA-GIS | Datatech The Farmer's Office | Delta Data Systems AGIS | ESRI ArcPad | EZ-Ranch | نرم‌افزار ایمیل | فیس‌بوک | Farm Business Software Systems Smart Feeder | Farm Files Crops | Farm Files Livestock | پایگاه‌های داده ذخیره‌سازی ماهی | سیستم‌های سیستم اطلاعات جغرافیایی GIS | سیستم پشتیبانی تحلیل منابع جغرافیایی GRASS | Global Mapper Software Global Mapper | نرم‌افزار سیستم موقعیت‌یاب جهانی GPS | سیستم‌های پایگاه داده مرکز تکثیر | Innovative Software Solutions Picas | International Response Technologies CowChip - Ranch House | John Deere Apex Farm Management | KELTEC Systems HerdMaster | Lion Edge Technologies Ranch Manager | MapInfo | MapShots EASi Suite | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Visio | Microsoft Word | Midwest MicroSystems Cow Sense | Oracle NetSuite | نرم‌افزار حقوق و دستمزد | Pear Technology Fieldman Farmer | PigCHAMP Care 3000 | ProducePak Mobile Farm Management | Red Wing Software CenterPoint Accounting for Agriculture | نرم‌افزار برنامه‌ریزی منابع | نرم‌افزار SAP | SST Development Group SSToolbox | SST Development Group Stratus | Sanders Software Consulting FarmBooks | Specialized Data Systems Ultra Farm | نرم‌افزار زمان‌بندی کارکنان | نرم‌افزار تحلیل آماری | Stenco Technologies Farm Trends | Sunrise Software CropSave | TapLogic FarmLogic | TatukGIS Editor | نرم‌افزار گزارش‌دهی زمان | Trimble AgGPS EZ-Map | Trimble Farm Works | Vertical Solutions Easy-Farm Accounting | نرم‌افزار مرورگر وب | ZedX AgFleet | i.Agri LandMark Farm</t>
+          <t>AGCO Advanced Technology Solutions Fieldstar | Accutech Systems Corporation AccuFarm-MGR | Adobe Photoshop | Advanced Veterinary Services Ranch Vision | Ag Connections Land.db | Ag Leader Technology SMS Advanced | AgData Blue Skies Accounting | AgTerra Technologies AgTrac | Agevo Farm Manager | AgriSoft/CMC AgriSoft/ERP | Alua Software Paddock Pro | AquaSoft Farm Manager | Argos Software ABECAS Insight | Atlassian Confluence | Brihzon Solutions SMART Dairy Resource Planning | CDA International Manifold System | CattleWorks | Cattlesoft CattleMax | Countryside Data Ag Payroll | Custom Software Group CSG AgroSys | DIVA-GIS | Datatech The Farmer's Office | Delta Data Systems AGIS | ESRI ArcPad | EZ-Ranch | نرم‌افزار ایمیل | Facebook | Farm Business Software Systems Smart Feeder | Farm Files Crops | Farm Files Livestock | پایگاه‌های داده ذخیره‌سازی ماهی | سیستم‌های سیستم اطلاعات جغرافیایی GIS | سیستم پشتیبانی تحلیل منابع جغرافیایی GRASS | Global Mapper Software Global Mapper | نرم‌افزار سیستم موقعیت‌یاب جهانی GPS | سیستم‌های پایگاه داده مرکز تکثیر | Innovative Software Solutions Picas | International Response Technologies CowChip - Ranch House | John Deere Apex Farm Management | KELTEC Systems HerdMaster | Lion Edge Technologies Ranch Manager | MapInfo | MapShots EASi Suite | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Visio | Microsoft Word | Midwest MicroSystems Cow Sense | Oracle NetSuite | نرم‌افزار حقوق و دستمزد | Pear Technology Fieldman Farmer | PigCHAMP Care 3000 | ProducePak Mobile Farm Management | Red Wing Software CenterPoint Accounting for Agriculture | نرم‌افزار برنامه‌ریزی منابع | نرم‌افزار SAP | SST Development Group SSToolbox | SST Development Group Stratus | Sanders Software Consulting FarmBooks | Specialized Data Systems Ultra Farm | نرم‌افزار زمان‌بندی کارکنان | نرم‌افزار تحلیل آماری | Stenco Technologies Farm Trends | Sunrise Software CropSave | TapLogic FarmLogic | TatukGIS Editor | نرم‌افزار گزارش‌دهی زمان | Trimble AgGPS EZ-Map | Trimble Farm Works | Vertical Solutions Easy-Farm Accounting | نرم‌افزار مرورگر وب | ZedX AgFleet | i.Agri LandMark Farm</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب | سخنوری | یادگیری فعال | نظارت | نوشتار</t>
+          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن | یادگیری فعال | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -974,17 +974,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک شنیداری | درک نوشتاری | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار | نظم‌دهی اطلاعات | بیان نوشتاری | دید نزدیک | روانی ایده‌ها | سرعت ادراکی | دید دور | انعطاف‌پذیری بستار | تجسم | اصالت | ثبات دست و بازو | توجه انتخابی | استدلال ریاضی</t>
+          <t>بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار | ترتیب‌دهی اطلاعات | بیان کتبی | بینایی نزدیک | روانی ایده‌ها | سرعت ادراکی | بینایی دور | انعطاف‌پذیری بستار | تجسم | اصالت | ثبات دست و بازو | توجه انتخابی | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>بحث‌های رودررو با افراد و درون تیم‌ها | محیط بیرونی، قرار گرفتن در معرض تمام شرایط آب و هوایی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه یا تیم کاری | تماس با دیگران | سلامت و ایمنی سایر کارکنان | محیط داخلی، بدون کنترل محیطی | مکالمات تلفنی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | محیط بیرونی، زیر پوشش | نتایج کاری و خروجی‌های سایر کارکنان | در یک وسیله نقلیه باز یا کار با تجهیزات | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | تناوب تصمیم‌گیری</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فضای باز، در معرض تمام شرایط آب و هوایی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | سلامت و ایمنی سایر کارکنان | محیط داخلی، بدون کنترل شرایط محیطی | مکالمات تلفنی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فضای باز، زیر سقف | پیامدهای کاری و نتایج سایر کارکنان | در یک وسیله نقلیه روباز یا کار با تجهیزات | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | فراوانی تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مهندسان کشاورزی | بازرسان کشاورزی | معلمان علوم کشاورزی، دوره پس از متوسطه | تکنسین‌های کشاورزی | پرورش‌دهندگان حیوانات | دانشمندان علوم دامی | تکنسین‌های فرآوری سوخت‌های زیستی | مدیران تولید سوخت‌های زیستی | خریداران و نمایندگان خرید، محصولات کشاورزی | مکانیک‌ها و تکنسین‌های خدمات تجهیزات کشاورزی | پیمانکاران نیروی کار مزرعه | کارگران و کارگران مزرعه، محصولات زراعی، نهالستان و گلخانه | کارگران مزرعه، دامداری و حیوانات آبزی | سرپرستان خط اول کارکنان کشاورزی، ماهیگیری و جنگلداری | دانشمندان و فناوران مواد غذایی | تکنسین‌های جنگل و حفاظت | مدیران تولید صنعتی | تکنسین‌های کشاورزی دقیق | مدیران مراتع | دانشمندان خاک و گیاه</t>
+          <t>مهندسان کشاورزی | بازرسان کشاورزی | مدرسان علوم کشاورزی، پس از متوسطه | تکنسین‌های کشاورزی | پرورش‌دهندگان حیوانات | دانشمندان علوم دامی | تکنسین‌های فرآوری سوخت‌های زیستی | مدیران تولید سوخت‌های زیستی | خریداران و نمایندگان خرید، محصولات کشاورزی | مکانیک‌ها و تکنسین‌های خدمات تجهیزات کشاورزی | پیمانکاران نیروی کار کشاورزی | کارگران کشاورزی و کارگران ساده، محصول، نهالستان و گلخانه | کارگران کشاورزی، حیوانات مزرعه، دامداری و آبزی‌پروری | سرپرستان خط اول کارکنان کشاورزی، ماهیگیری و جنگل‌داری | دانشمندان و تکنولوژیست‌های علوم غذایی | تکنسین‌های جنگل و حفاظت | مدیران تولید صنعتی | تکنسین‌های کشاورزی دقیق | مدیران مراتع | دانشمندان خاک و گیاه</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1016,32 +1016,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3M Post-it App | AEC Software FastTrack Schedule | Adobe Acrobat | نرم‌افزار Adobe Creative Cloud | ArenaSoft Estimating | Autodesk AutoCAD | Autodesk AutoCAD Civil 3D | Autodesk Revit | Axios Systems assyst | Bechtel Software SETROUTE | CBS ProLog Manager | CSI WSE CodeBuddy | Cadsoft Design/Build | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | Daily Manager | نرم‌افزار پایگاه داده | نرم‌افزار تصویربرداری پهپاد | Dropbox | نرم‌افزار ایمیل | Explorer Engineer | Google Docs | Google Drive | HCSS HeavyBid | HCSS HeavyJob | نرم‌افزار IMPACT | ISS Construction Manager | نرم‌افزار یکپارچه مدیریت ساخت‌وساز | Jobber Computer Plus | LinkedIn | Lombardi Teamworks | Loom | Microsoft Access | Microsoft Dynamics | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SharePoint | Microsoft Visio | Microsoft Word | Oracle JD Edwards EnterpriseOne | Oracle Primavera Enterprise Project Portfolio Management | نرم‌افزار Procore | Profitool GearWatch | نرم‌افزار Profitool (ویژگی منابع انسانی) | نرم‌افزار Profitool (ویژگی حسابداری زمان) | Quantum Software Solutions Quantum Project Manager | نرم‌افزار مدیریت کسب‌وکار QuickBase | نرم‌افزار SAP | SRC Cash Flow Forecasting | Sage 100 Contractor | Sage 300 Construction and Real Estate | نرم‌افزار زمان‌بندی | Site Manager | نرم‌افزار کنترل نظارتی و جمع‌آوری داده SCADA | Trimble SketchUp Pro | UDA Technologies ConstructionSuite | VirtualBoss | نرم‌افزار Yardi</t>
+          <t>3M Post-it App | AEC Software FastTrack Schedule | Adobe Acrobat | نرم‌افزار Adobe Creative Cloud | ArenaSoft Estimating | Autodesk AutoCAD | Autodesk AutoCAD Civil 3D | Autodesk Revit | Axios Systems assyst | Bechtel Software SETROUTE | CBS ProLog Manager | CSI WSE CodeBuddy | Cadsoft Design/Build | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | Daily Manager | نرم‌افزار پایگاه داده | نرم‌افزار تصویربرداری پهپاد | Dropbox | نرم‌افزار ایمیل | Explorer Engineer | Google Docs | Google Drive | HCSS HeavyBid | HCSS HeavyJob | نرم‌افزار IMPACT | ISS Construction Manager | نرم‌افزار یکپارچه مدیریت ساخت‌وساز | Jobber Computer Plus | LinkedIn | Lombardi Teamworks | Loom | Microsoft Access | Microsoft Dynamics | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SharePoint | Microsoft Visio | Microsoft Word | Oracle JD Edwards EnterpriseOne | Oracle Primavera Enterprise Project Portfolio Management | Procore software | Profitool GearWatch | نرم‌افزار Profitool (ویژگی منابع انسانی) | نرم‌افزار Profitool (ویژگی حسابداری زمان) | Quantum Software Solutions Quantum Project Manager | نرم‌افزار مدیریت کسب‌وکار QuickBase | نرم‌افزار SAP | SRC Cash Flow Forecasting | Sage 100 Contractor | Sage 300 Construction and Real Estate | نرم‌افزار زمان‌بندی | Site Manager | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | Trimble SketchUp Pro | UDA Technologies ConstructionSuite | VirtualBoss | نرم‌افزار Yardi</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | سخنوری | یادگیری فعال | نظارت | نوشتار | ریاضیات | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | سخن گفتن | یادگیری فعال | نظارت | نگارش | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ساختمان و ساخت‌وساز | مدیریت و اداره | ریاضیات | مهندسی و فناوری | خدمات مشتری و شخصی | مکانیک | تولید و فرآوری | اقتصاد و حسابداری | ایمنی و امنیت عمومی | پرسنل و منابع انسانی | طراحی | زبان انگلیسی | اداری | کامپیوتر و الکترونیک | آموزش و پرورش | قانون و دولت | فروش و بازاریابی</t>
+          <t>ساختمان و ساخت‌وساز | مدیریت و اداره | ریاضیات | مهندسی و فناوری | خدمات مشتری و شخصی | مکانیک | تولید و فرآوری | اقتصاد و حسابداری | ایمنی و امنیت عمومی | پرسنل و منابع انسانی | طراحی | زبان انگلیسی | اداری | رایانه و الکترونیک | آموزش و پرورش | قانون و دولت | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شنیداری | درک نوشتاری | بیان شفاهی | استدلال قیاسی | نظم‌دهی اطلاعات | بیان نوشتاری | استدلال استقرایی | تجسم | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | دید دور | انعطاف‌پذیری بستار | استدلال ریاضی | روانی ایده‌ها | توجه انتخابی | توانایی عددی | سرعت بستار | اصالت | تشخیص رنگ بصری | اشتراک زمانی | سرعت ادراکی</t>
+          <t>حساسیت به مسئله | درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | ترتیب‌دهی اطلاعات | بیان کتبی | استدلال استقرایی | تجسم | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | بینایی دور | انعطاف‌پذیری بستار | استدلال ریاضی | روانی ایده‌ها | توجه انتخابی | توانایی عددی | سرعت بستار | اصالت | تشخیص رنگ بصری | تقسیم توجه | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های رودررو با افراد و درون تیم‌ها | تماس با دیگران | کار با یا مشارکت در یک گروه یا تیم کاری | استفاده از تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | سلامت و ایمنی سایر کارکنان | فشار زمانی | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | تناوب تصمیم‌گیری | اهمیت دقیق یا صحیح بودن | قرار گرفتن در معرض صدا، سطوح نویز که حواس‌پرت‌کن یا ناراحت‌کننده هستند | تعیین وظایف، اولویت‌ها و اهداف | تعامل با مشتریان خارجی یا عموم مردم | محیط داخلی، بدون کنترل محیطی | محیط بیرونی، قرار گرفتن در معرض تمام شرایط آب و هوایی | نتایج کاری و خروجی‌های سایر کارکنان | محیط داخلی، دارای کنترل محیطی | نامه‌ها و یادداشت‌های کتبی | صرف زمان برای ایستادن | سطح رقابت | پیامد خطا | نزدیکی فیزیکی</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | سلامت و ایمنی سایر کارکنان | فشار زمانی | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فراوانی تصمیم‌گیری | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | تعیین وظایف، اولویت‌ها و اهداف | تعامل با مشتریان خارجی یا عموم مردم | محیط داخلی، بدون کنترل شرایط محیطی | فضای باز، در معرض تمام شرایط آب و هوایی | پیامدهای کاری و نتایج سایر کارکنان | محیط داخلی، دارای کنترل شرایط محیطی | نامه‌ها و یادداشت‌های کتبی | صرف زمان برای ایستادن | سطح رقابت | پیامد خطا | نزدیکی فیزیکی</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>معماران، به جز منظر و دریایی | مدیران معماری و مهندسی | تکنسین‌ها و تکنولوژیست‌های مهندسی عمران | مهندسان عمران | بازرسان ساخت‌وساز و ساختمان | برآوردکنندگان هزینه | مدیران تأسیسات | سرپرستان خط اول مشاغل ساخت‌وساز و استخراج | سرپرستان خط اول کارکنان محوطه‌سازی، خدمات چمن و نگهداری زمین | سرپرستان خط اول مکانیک‌ها، نصاب‌ها و تعمیرکاران | مدیران عمومی و عملیات | مدیران تولید زمین‌گرمایی | بازرسان و محققان اموال دولتی | مهندسان صنایع | مدیران تولید صنعتی | کارگران نگهداری و تعمیرات، عمومی | مهندسان مکانیک | متخصصان مدیریت پروژه | مدیران نصب انرژی خورشیدی | مدیران توسعه انرژی باد</t>
+          <t>معماران، به‌جز منظر و دریایی | مدیران معماری و مهندسی | تکنسین‌ها و کارشناسان مهندسی عمران | مهندسان عمران | بازرسان ساختمان و ساخت‌وساز | برآوردکنندگان هزینه | مدیران تسهیلات | سرپرستان خط اول مشاغل ساختمانی و کارگران استخراج | سرپرستان خط اول کارگران فضای سبز، خدمات چمن‌زنی و نگهداری محوطه | سرپرستان خط اول مکانیک‌ها، نصابان و تعمیرکاران | مدیران عمومی و عملیات | مدیران تولید زمین‌گرمایی | بازرسان و محققان اموال دولتی | مهندسان صنایع | مدیران تولید صنعتی | کارگران نگهداری و تعمیرات عمومی | مهندسان مکانیک | متخصصان مدیریت پروژه | مدیران نصب انرژی خورشیدی | مدیران توسعه انرژی بادی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0003_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0003_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | درک مطلب | شنیدن فعال | نظارت | یادگیری فعال | نگارش | ریاضیات | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | درک مطلب | گوش دادن فعال | نظارت | یادگیری فعال | نگارش | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>مکانیک | مهندسی و فناوری | تولید و فرآوری | مدیریت و امور اداری | پرسنلی و منابع انسانی | ایمنی و امنیت عمومی | اداری | آموزش و تدریس | ریاضیات | رایانه و الکترونیک | شیمی | زبان انگلیسی | طراحی | فیزیک | اقتصاد و حسابداری | ساختمان و سازه</t>
+          <t>مکانیک | مهندسی و فناوری | تولید و فرآوری | مدیریت و اداره | پرسنل و منابع انسانی | ایمنی و امنیت عمومی | اداری | آموزش و پرورش | ریاضیات | رایانه و الکترونیک | شیمی | زبان انگلیسی | طراحی | فیزیک | اقتصاد و حسابداری | ساختمان و ساخت‌وساز</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بیان کتبی | مرتب‌سازی اطلاعات | دید نزدیک | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری طبقه‌بندی | انعطاف‌پذیری بستن ذهنی | دید دور | تسهیلات محاسباتی | روانی ایده‌ها | توجه انتخابی | سرعت ادراک | سرعت بستن ذهنی | استدلال ریاضی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بیان کتبی | ترتیب‌دهی اطلاعات | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | بینایی دور | توانایی عددی | روانی ایده‌ها | توجه انتخابی | سرعت ادراکی | سرعت بستار | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>تکنسین‌های فرآوری سوخت‌های زیستی | مدیران تولید سوخت‌های زیستی | مدیران توسعه محصول و فناوری بیودیزل/سوخت‌های زیستی | تکنسین‌های نیروگاه زیست‌توده | متصدیان سیستم‌ها و کارخانه‌های شیمیایی | مهندسان انرژی، به‌جز باد و خورشید | متصدیان تاسیسات گاز | مدیران تولید زمین‌گرمایی | تکنسین‌های زمین‌گرمایی | تکنسین‌های نیروگاه‌های برق‌آبی | مدیران تولید برق‌آبی | مهندسان صنایع | مدیران تولید صنعتی | متصدیان سیستم‌های پمپاژ نفت، متصدیان پالایشگاه و سنجش‌گران | توزیع‌کنندگان و دیسپچرهای برق | متصدیان نیروگاه‌های برق | مهندسان تاسیسات و متصدیان دیگ‌های بخار | متصدیان سیستم‌ها و تصفیه‌خانه‌های آب و فاضلاب | مدیران عملیات انرژی بادی | تکنسین‌های تعمیر و نگهداری توربین‌های بادی</t>
+          <t>تکنسین‌های فراوری سوخت‌های زیستی | مدیران تولید سوخت‌های زیستی | مدیران توسعه محصول و فناوری زیست‌سوخت | تکنسین‌های نیروگاه زیست‌توده | اپراتورهای تأسیسات و سیستم‌های فرایندی صنایع شیمیایی | مهندسان انرژی، به‌جز بادی و خورشیدی | اپراتورهای تأسیسات و پالایشگاه‌های گاز | مدیران تولید انرژی زمین‌گرمایی | تکنسین‌های سامانه‌های زمین‌گرمایی | تکنسین‌های نیروگاه برقابی | مدیران تولید نیروگاه‌های برق‌آبی | مهندسان صنایع | مدیران تولید صنعتی | اپراتورهای پمپ‌های انتقال نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | دیسپچرها و توزیع‌کنندگان شبکه برق | اپراتورهای نیروگاه برق | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب | مدیران بهره‌برداری و تعمیرات نیروگاه‌های بادی | تکنسین‌های تعمیر و نگهداری توربین‌های بادی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | نظارت | تفکر انتقادی | یادگیری فعال | استراتژی‌های یادگیری | نگارش | علوم | ریاضیات</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نظارت | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | نگارش | علوم | ریاضیات</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>مکانیک | ایمنی و امنیت عمومی | مدیریت و امور اداری | زبان انگلیسی | مهندسی و فناوری | رایانه و الکترونیک | پرسنلی و منابع انسانی | آموزش و تدریس | ریاضیات | حقوق و مقررات دولتی | اداری | طراحی | فیزیک | تولید و فرآوری | روان‌شناسی</t>
+          <t>مکانیک | ایمنی و امنیت عمومی | مدیریت و اداره | زبان انگلیسی | مهندسی و فناوری | رایانه و الکترونیک | پرسنل و منابع انسانی | آموزش و پرورش | ریاضیات | قانون و دولت | اداری | طراحی | فیزیک | تولید و فرآوری | روان‌شناسی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بیان کتبی | سرعت ادراک | تشخیص گفتار | وضوح گفتار | دید نزدیک | مرتب‌سازی اطلاعات | روانی ایده‌ها | استدلال ریاضی | انعطاف‌پذیری طبقه‌بندی | تسهیلات محاسباتی | انعطاف‌پذیری بستن ذهنی | تجسم فضایی | توجه انتخابی | تمایز رنگ‌ها | تسهیم زمان | ابتکار و اصالت</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بیان کتبی | سرعت ادراکی | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | ترتیب‌دهی اطلاعات | روانی ایده‌ها | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | توانایی عددی | انعطاف‌پذیری بستار | تجسم | توجه انتخابی | تشخیص رنگ بصری | تقسیم توجه | اصالت</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مدیران تولید سوخت‌های زیستی | مدیران توسعه محصول و فناوری بیودیزل/سوخت‌های زیستی | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه‌های زیست‌توده | مهندسان برق | مهندسان انرژی، به‌جز باد و خورشید | متصدیان تاسیسات گاز | مدیران تولید زمین‌گرمایی | تکنسین‌های زمین‌گرمایی | تکنسین‌های نیروگاه‌های برق‌آبی | مدیران تولید صنعتی | توزیع‌کنندگان و دیسپچرهای برق | متصدیان نیروگاه‌های برق | مهندسان سیستم‌های انرژی خورشیدی | متصدیان سیستم‌ها و تصفیه‌خانه‌های آب و فاضلاب | مهندسان آب و فاضلاب | مدیران توسعه پروژه‌های انرژی بادی | مهندسان انرژی بادی | مدیران عملیات انرژی بادی | تکنسین‌های تعمیر و نگهداری توربین‌های بادی</t>
+          <t>مدیران تولید سوخت‌های زیستی | مدیران توسعه محصول و فناوری زیست‌سوخت | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه‌های زیست‌توده | مهندسان برق | مهندسان انرژی، به‌جز بادی و خورشیدی | اپراتورهای تأسیسات و پالایشگاه‌های گاز | مدیران تولید انرژی زمین‌گرمایی | تکنسین‌های سامانه‌های زمین‌گرمایی | تکنسین‌های نیروگاه برقابی | مدیران تولید صنعتی | دیسپچرها و توزیع‌کنندگان شبکه برق | اپراتورهای نیروگاه برق | مهندسان سیستم‌های انرژی خورشیدی | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب | مهندسان آب و فاضلاب | مدیران توسعه پروژه‌های انرژی بادی | مهندسان انرژی باد | مدیران بهره‌برداری و تعمیرات نیروگاه‌های بادی | تکنسین‌های تعمیر و نگهداری توربین‌های بادی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | نگارش | نظارت | تفکر انتقادی | یادگیری فعال | ریاضیات | استراتژی‌های یادگیری</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | نظارت | تفکر انتقادی | یادگیری فعال | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | زبان انگلیسی | حقوق و مقررات دولتی | اقتصاد و حسابداری | رایانه و الکترونیک | ریاضیات | اداری | پرسنلی و منابع انسانی | آموزش و تدریس</t>
+          <t>مدیریت و اداره | خدمات مشتری و شخصی | زبان انگلیسی | قانون و دولت | اقتصاد و حسابداری | رایانه و الکترونیک | ریاضیات | اداری | پرسنل و منابع انسانی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | درک کتبی | روانی ایده‌ها | بیان کتبی | مرتب‌سازی اطلاعات | استدلال استقرایی | حساسیت به مسئله | ابتکار و اصالت | تسهیلات محاسباتی | توجه انتخابی | دید نزدیک | استدلال ریاضی | انعطاف‌پذیری طبقه‌بندی</t>
+          <t>درک شفاهی | بیان شفاهی | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | درک کتبی | روانی ایده‌ها | بیان کتبی | ترتیب‌دهی اطلاعات | استدلال استقرایی | حساسیت به مسئله | اصالت | توانایی عددی | توجه انتخابی | بینایی نزدیک | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | تحلیل‌گران هوش تجاری | خریداران و کارشناسان خرید محصولات کشاورزی | سرپرستان رده‌اول کارکنان فروش غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان پشتیبانی اداری و دفتری | مدیران عامل و مدیران عملیاتی | مدیران تولید صنعتی | کارشناسان لجستیک | تحلیل‌گران لجستیک | مهندسان لجستیک | تحلیل‌گران مدیریت | مدیران بازاریابی | کارمندان تدارکات و کارپردازان | کارمندان برنامه‌ریزی تولید، تدارکات و پیگیری | کارشناسان خرید، به‌جز محصولات عمده‌فروشی، خرده‌فروشی و کشاورزی | مدیران فروش | نمایندگان فروش خدمات، به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری | مدیران زنجیره تامین | مدیران حمل‌ونقل، انبارداری و توزیع | خریداران عمده و خرده‌فروشی، به‌جز محصولات کشاورزی</t>
+          <t>مدیران خدمات اداری و پشتیبانی | تحلیل‌گران هوش تجاری | خریداران و کارشناسان خرید محصولات کشاورزی | سرپرستان رده‌اول فروشندگان عمده‌فروشی و غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | مدیران کل و مدیران عملیات | مدیران تولید صنعتی | کارشناسان لجستیک و مدیریت زنجیره تأمین | تحلیل‌گران لجستیک و فرایند توزیع | مهندسان لجستیک و زنجیره تأمین | کارشناسان تحلیل مدیریت و روش‌ها | مدیران بازاریابی | کارمندان تدارکات و کارپردازی | کارشناسان و کارمندان برنامه‌ریزی تولید و پیگیری امور | کارشناسان خرید و امور قراردادها | مدیران فروش | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | مدیران زنجیره تامین | مدیران حمل‌ونقل، انبارداری و توزیع | خریداران عمده‌فروشی و خرده‌فروشی کالاهای غیرکشاورزی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | نظارت | یادگیری فعال | نگارش | سخن گفتن | تفکر انتقادی | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | گوش دادن فعال | نظارت | یادگیری فعال | نگارش | سخن گفتن | تفکر انتقادی | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>حمل‌ونقل | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | زبان انگلیسی | ریاضیات | پرسنلی و منابع انسانی | ایمنی و امنیت عمومی | اقتصاد و حسابداری | رایانه و الکترونیک | تولید و فرآوری | حقوق و مقررات دولتی | اداری | آموزش و تدریس</t>
+          <t>حمل و نقل | مدیریت و اداره | خدمات مشتری و شخصی | زبان انگلیسی | ریاضیات | پرسنل و منابع انسانی | ایمنی و امنیت عمومی | اقتصاد و حسابداری | رایانه و الکترونیک | تولید و فرآوری | قانون و دولت | اداری | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بیان شفاهی | مرتب‌سازی اطلاعات | انعطاف‌پذیری طبقه‌بندی | دید نزدیک | وضوح گفتار | تشخیص گفتار | روانی ایده‌ها | ابتکار و اصالت | انعطاف‌پذیری بستن ذهنی | دید دور</t>
+          <t>درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بیان شفاهی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | روانی ایده‌ها | اصالت | انعطاف‌پذیری بستار | بینایی دور</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>سرپرستان بارگیری و تخلیه بارهای هوایی | کارشناسان و متصدیان باربری و حمل کالا | دیسپچرهای ترابری، به‌جز پلیس، آتش‌نشانی و اورژانس | مدیران تاسیسات و اماکن | سرپرستان رده‌اول کارگران و جابه‌جا‌کنندگان دستی کالا | سرپرستان رده‌اول متصدیان ماشین‌آلات و ناوگان حمل بار | سرپرستان رده‌اول مهمانداران و خدمه مسافری | فورواردرهای بار و محموله | مدیران عامل و مدیران عملیاتی | مدیران تولید صنعتی | کارشناسان لجستیک | تحلیل‌گران لجستیک | مهندسان لجستیک | تحلیل‌گران مدیریت | کارمندان برنامه‌ریزی تولید، تدارکات و پیگیری | کارشناسان مدیریت پروژه | مدیران خرید و تدارکات | انبارداران، مأموران ورود و خروج و کارمندان کنترل موجودی | مدیران زنجیره تامین | برنامه‌ریزان حمل‌ونقل</t>
+          <t>سرپرستان بارگیری و جابه‌جایی بار هواپیما | کارگزاران حمل‌ونقل و بار | متصدیان دیسپاچ و اعزام | مدیران امور ساختمان و تأسیسات | سرپرستان رده‌اول کارگران ساده و جابه‌جاکنندگان دستی بار | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | سرپرستان رده‌اول مهمانداران و خدمه مسافری | کارشناسان و متصدیان فورواردری و حمل‌ونقل بین‌المللی کالا | مدیران کل و مدیران عملیات | مدیران تولید صنعتی | کارشناسان لجستیک و مدیریت زنجیره تأمین | تحلیل‌گران لجستیک و فرایند توزیع | مهندسان لجستیک و زنجیره تأمین | کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان و کارمندان برنامه‌ریزی تولید و پیگیری امور | کارشناسان مدیریت پروژه | مدیران خرید و تدارکات | کارمندان انبار، ارسال و دریافت کالا | مدیران زنجیره تامین | برنامه‌ریزان سیستم‌های حمل‌ونقل</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>نظارت | سخن گفتن | شنیدن فعال | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | استراتژی‌های یادگیری | ریاضیات</t>
+          <t>نظارت | سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>حمل‌ونقل | مدیریت و امور اداری | زبان انگلیسی | اقتصاد و حسابداری | خدمات مشتریان و خدمات فردی | تولید و فرآوری | پرسنلی و منابع انسانی | ریاضیات | رایانه و الکترونیک | بازاریابی و فروش</t>
+          <t>حمل و نقل | مدیریت و اداره | زبان انگلیسی | اقتصاد و حسابداری | خدمات مشتری و شخصی | تولید و فرآوری | پرسنل و منابع انسانی | ریاضیات | رایانه و الکترونیک | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | انعطاف‌پذیری طبقه‌بندی | وضوح گفتار | دید نزدیک | تشخیص گفتار | ابتکار و اصالت | توجه انتخابی | استدلال ریاضی | روانی ایده‌ها | انعطاف‌پذیری بستن ذهنی | تسهیلات محاسباتی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | بینایی نزدیک | تشخیص گفتار | اصالت | توجه انتخابی | استدلال ریاضی | روانی ایده‌ها | انعطاف‌پذیری بستار | توانایی عددی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>خریداران و کارشناسان خرید محصولات کشاورزی | سرپرستان رده‌اول متصدیان ماشین‌آلات و ناوگان حمل بار | مدیران عامل و مدیران عملیاتی | مهندسان صنایع | مدیران تولید صنعتی | کارشناسان لجستیک | تحلیل‌گران لجستیک | مهندسان لجستیک | تحلیل‌گران مدیریت | مهندسان ساخت و تولید | مدیران بازاریابی | کارمندان تدارکات و کارپردازان | کارمندان برنامه‌ریزی تولید، تدارکات و پیگیری | کارشناسان مدیریت پروژه | کارشناسان خرید، به‌جز محصولات عمده‌فروشی، خرده‌فروشی و کشاورزی | مدیران خرید و تدارکات | نمایندگان فروش عمده و صنعتی، محصولات علمی و تخصصی | انبارداران، مأموران ورود و خروج و کارمندان کنترل موجودی | مدیران حمل‌ونقل، انبارداری و توزیع | خریداران عمده و خرده‌فروشی، به‌جز محصولات کشاورزی</t>
+          <t>خریداران و کارشناسان خرید محصولات کشاورزی | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | مدیران کل و مدیران عملیات | مهندسان صنایع | مدیران تولید صنعتی | کارشناسان لجستیک و مدیریت زنجیره تأمین | تحلیل‌گران لجستیک و فرایند توزیع | مهندسان لجستیک و زنجیره تأمین | کارشناسان تحلیل مدیریت و روش‌ها | مهندسان تولید و ساخت | مدیران بازاریابی | کارمندان تدارکات و کارپردازی | کارشناسان و کارمندان برنامه‌ریزی تولید و پیگیری امور | کارشناسان مدیریت پروژه | کارشناسان خرید و امور قراردادها | مدیران خرید و تدارکات | کارشناسان فروش عمده و صنعتی کالاهای فنی و علمی | کارمندان انبار، ارسال و دریافت کالا | مدیران حمل‌ونقل، انبارداری و توزیع | خریداران عمده‌فروشی و خرده‌فروشی کالاهای غیرکشاورزی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>سخن گفتن | نگارش | شنیدن فعال | درک مطلب | تفکر انتقادی | یادگیری فعال | نظارت | استراتژی‌های یادگیری | ریاضیات</t>
+          <t>سخن گفتن | نگارش | گوش دادن فعال | درک مطلب | تفکر انتقادی | یادگیری فعال | نظارت | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>پرسنلی و منابع انسانی | زبان انگلیسی | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | اقتصاد و حسابداری | ریاضیات | حقوق و مقررات دولتی | اداری</t>
+          <t>پرسنل و منابع انسانی | زبان انگلیسی | مدیریت و اداره | خدمات مشتری و شخصی | اقتصاد و حسابداری | ریاضیات | قانون و دولت | اداری</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>بیان کتبی | درک شفاهی | درک کتبی | بیان شفاهی | وضوح گفتار | حساسیت به مسئله | تشخیص گفتار | استدلال قیاسی | دید نزدیک | استدلال استقرایی | استدلال ریاضی | روانی ایده‌ها | تسهیلات محاسباتی | انعطاف‌پذیری طبقه‌بندی | مرتب‌سازی اطلاعات | ابتکار و اصالت</t>
+          <t>بیان کتبی | درک شفاهی | درک کتبی | بیان شفاهی | وضوح گفتار | حساسیت به مسئله | تشخیص گفتار | استدلال قیاسی | بینایی نزدیک | استدلال استقرایی | استدلال ریاضی | روانی ایده‌ها | توانایی عددی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | اصالت</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | مدیران خدمات اداری | تحلیل‌گران بودجه | مدیران عامل | کارشناسان جبران خدمت، مزایا و طبقه‌بندی مشاغل | مدیران انطباق و نظارت قانونی | مصاحبه‌کنندگان صلاحیت متقاضیان، برنامه‌های دولتی | کارشناسان و بازرسان تساوی فرصت‌های شغلی | بازرسان مالی | مدیران مالی | سرپرستان رده‌اول کارکنان پشتیبانی اداری و دفتری | کارمندان امور پرسنلی و اداری، به‌جز حقوق و دستمزد و حضور و غیاب | مدیران منابع انسانی | کارشناسان منابع انسانی | کارشناسان روابط کار | تحلیل‌گران مدیریت | مدیران خدمات درمانی و سلامت | متصدیان ثبت کارکرد، حضور و غیاب و حقوق و دستمزد | مدیران خدمات اجتماعی و رفاهی | خزانه‌داران و مدیران امور مالی</t>
+          <t>حسابداران و حسابرسان | مدیران خدمات اداری و پشتیبانی | تحلیل‌گران بودجه | مدیران عامل و مدیران ارشد اجرایی | کارشناسان جبران خدمت، مزایا و طبقه‌بندی مشاغل | مدیران تطبیق و نظارت مقرراتی | کارشناسان مصاحبه و احراز صلاحیت متقاضیان طرح‌های حمایتی و دولتی | کارشناسان امور انطباق و صیانت از فرصت‌های برابر استخدامی | بازرسان و ارزیابان مالی | مدیران امور مالی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت ساعات کار | مدیران منابع انسانی | کارشناسان منابع انسانی | کارشناسان روابط کار و امور تشکل‌های کارگری | کارشناسان تحلیل مدیریت و روش‌ها | مدیران خدمات درمانی و بهداشتی | کارمندان امور حقوق، دستمزد و ثبت زمان | مدیران خدمات اجتماعی و خدمات مردمی | خزانه‌داران و مدیران مالی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | نگارش | نظارت | یادگیری فعال | تفکر انتقادی | استراتژی‌های یادگیری | ریاضیات</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نگارش | نظارت | یادگیری فعال | تفکر انتقادی | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>پرسنلی و منابع انسانی | زبان انگلیسی | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | آموزش و تدریس | حقوق و مقررات دولتی | روان‌شناسی | ایمنی و امنیت عمومی | رایانه و الکترونیک | ارتباطات و رسانه | ریاضیات</t>
+          <t>پرسنل و منابع انسانی | زبان انگلیسی | مدیریت و اداره | خدمات مشتری و شخصی | آموزش و پرورش | قانون و دولت | روان‌شناسی | ایمنی و امنیت عمومی | رایانه و الکترونیک | ارتباطات و رسانه | ریاضیات</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | دید نزدیک | تشخیص گفتار | حساسیت به مسئله | روانی ایده‌ها | ابتکار و اصالت | مرتب‌سازی اطلاعات | توجه انتخابی | انعطاف‌پذیری طبقه‌بندی | سرعت بستن ذهنی | به‌خاطرسپاری | تسهیلات محاسباتی | استدلال ریاضی</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | تشخیص گفتار | حساسیت به مسئله | روانی ایده‌ها | اصالت | ترتیب‌دهی اطلاعات | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | سرعت بستار | حفظ کردن | توانایی عددی | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | مدیران عامل | مدیران جبران خدمت و مزایا | کارشناسان جبران خدمت، مزایا و طبقه‌بندی مشاغل | مدیران انطباق و نظارت قانونی | مصاحبه‌کنندگان صلاحیت متقاضیان، برنامه‌های دولتی | کارشناسان و بازرسان تساوی فرصت‌های شغلی | سرپرستان رده‌اول کارکنان پشتیبانی اداری و دفتری | کارمندان امور پرسنلی و اداری، به‌جز حقوق و دستمزد و حضور و غیاب | کارشناسان منابع انسانی | روان‌شناسان سازمانی و صنعتی | کارشناسان روابط کار | تحلیل‌گران مدیریت | مدیران خدمات درمانی و سلامت | متصدیان ثبت کارکرد، حضور و غیاب و حقوق و دستمزد | کارشناسان مدیریت پروژه | مدیران روابط عمومی | مدیران خدمات اجتماعی و رفاهی | مدیران آموزش و بهسازی | کارشناسان آموزش و بهسازی</t>
+          <t>مدیران خدمات اداری و پشتیبانی | مدیران عامل و مدیران ارشد اجرایی | مدیران جبران خدمت و مزایا | کارشناسان جبران خدمت، مزایا و طبقه‌بندی مشاغل | مدیران تطبیق و نظارت مقرراتی | کارشناسان مصاحبه و احراز صلاحیت متقاضیان طرح‌های حمایتی و دولتی | کارشناسان امور انطباق و صیانت از فرصت‌های برابر استخدامی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت ساعات کار | کارشناسان منابع انسانی | روان‌شناسان صنعتی و سازمانی | کارشناسان روابط کار و امور تشکل‌های کارگری | کارشناسان تحلیل مدیریت و روش‌ها | مدیران خدمات درمانی و بهداشتی | کارمندان امور حقوق، دستمزد و ثبت زمان | کارشناسان مدیریت پروژه | مدیران روابط عمومی | مدیران خدمات اجتماعی و خدمات مردمی | مدیران آموزش و بهسازی | کارشناسان آموزش و توسعه منابع انسانی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>استراتژی‌های یادگیری | سخن گفتن | شنیدن فعال | درک مطلب | نگارش | نظارت | تفکر انتقادی | یادگیری فعال</t>
+          <t>راهبردهای یادگیری | سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | نظارت | تفکر انتقادی | یادگیری فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | زبان انگلیسی | مدیریت و امور اداری | پرسنلی و منابع انسانی | خدمات مشتریان و خدمات فردی | ارتباطات و رسانه | روان‌شناسی | رایانه و الکترونیک</t>
+          <t>آموزش و پرورش | زبان انگلیسی | مدیریت و اداره | پرسنل و منابع انسانی | خدمات مشتری و شخصی | ارتباطات و رسانه | روان‌شناسی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | روانی ایده‌ها | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | دید نزدیک | ابتکار و اصالت | حساسیت به مسئله | استدلال استقرایی | مرتب‌سازی اطلاعات | انعطاف‌پذیری طبقه‌بندی</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | روانی ایده‌ها | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | اصالت | حساسیت به مسئله | استدلال استقرایی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>هنرآموزان و معلمان آموزش‌های فنی و حرفه‌ای دوره اول متوسطه | مدرسان آموزش‌های فنی و حرفه‌ای پسامتوسطه | مدیران آموزشی دوره‌های ابتدایی و متوسطه | مدیران آموزشی مراکز دانشگاهی و آموزش عالی | مدرسان علوم تربیتی آموزش عالی | مدیران مراکز پیش‌دبستانی و مهدهای کودک | مشاوران و راهنمایان تحصیلی، شغلی و تربیتی | سرپرستان رده‌اول کارکنان سرگرمی و تفریحات، به‌جز خدمات شرط‌بندی | کارمندان امور پرسنلی و اداری، به‌جز حقوق و دستمزد و حضور و غیاب | مدیران منابع انسانی | کارشناسان منابع انسانی | روان‌شناسان سازمانی و صنعتی | هماهنگ‌کنندگان برنامه‌ها و دوره‌های آموزشی | تحلیل‌گران مدیریت | مدیران خدمات درمانی و سلامت | کارشناسان مدیریت پروژه | مشاوران توان‌بخشی | مدیران خدمات اجتماعی و رفاهی | معلمان آموزش استثنایی دوره پیش‌دبستانی | کارشناسان آموزش و بهسازی</t>
+          <t>معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | مدرسان آموزش‌های فنی و حرفه‌ای در آموزش عالی | مدیران آموزشی مقاطع ابتدایی و متوسطه | مدیران آموزش عالی | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | مدیران مراکز آموزشی و مراقبت از کودک، پیش‌دبستانی و مهدکودک | مشاوران تحصیلی، شغلی و هدایت استعدادها | سرپرستان رده‌اول کارکنان مراکز تفریحی و سرگرمی، به‌جز بازی‌های شرط‌بندی | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت ساعات کار | مدیران منابع انسانی | کارشناسان منابع انسانی | روان‌شناسان صنعتی و سازمانی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | کارشناسان تحلیل مدیریت و روش‌ها | مدیران خدمات درمانی و بهداشتی | کارشناسان مدیریت پروژه | مشاوران توانبخشی | مدیران خدمات اجتماعی و خدمات مردمی | معلمان آموزش استثنایی دوره آمادگی و نوآموزان | کارشناسان آموزش و توسعه منابع انسانی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن | یادگیری فعال | نظارت | نگارش</t>
+          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن | یادگیری فعال | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | تولید و فرآوری | زیست‌شناسی | ریاضیات | زبان انگلیسی | پرسنلی و منابع انسانی | صنایع غذایی و تولید خوراک | اقتصاد و حسابداری | بازاریابی و فروش | مکانیک | خدمات مشتریان و خدمات فردی | آموزش و تدریس | شیمی</t>
+          <t>مدیریت و اداره | تولید و فرآوری | زیست‌شناسی | ریاضیات | زبان انگلیسی | پرسنل و منابع انسانی | تولید مواد غذایی | اقتصاد و حسابداری | فروش و بازاریابی | مکانیک | خدمات مشتری و شخصی | آموزش و پرورش | شیمی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | انعطاف‌پذیری طبقه‌بندی | وضوح گفتار | تشخیص گفتار | مرتب‌سازی اطلاعات | بیان کتبی | دید نزدیک | روانی ایده‌ها | سرعت ادراک | دید دور | انعطاف‌پذیری بستن ذهنی | تجسم فضایی | ابتکار و اصالت | ثبات دست و بازو | توجه انتخابی | استدلال ریاضی</t>
+          <t>بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار | ترتیب‌دهی اطلاعات | بیان کتبی | بینایی نزدیک | روانی ایده‌ها | سرعت ادراکی | بینایی دور | انعطاف‌پذیری بستار | تجسم | اصالت | ثبات دست و بازو | توجه انتخابی | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مهندسان کشاورزی | بازرسان امور کشاورزی | اساتید علوم کشاورزی در دانشگاه‌ها و آموزش عالی | تکنسین‌های کشاورزی | اصلاح‌کنندگان نژاد دام و طیور | متخصصان علوم دامی | تکنسین‌های فرآوری سوخت‌های زیستی | مدیران تولید سوخت‌های زیستی | خریداران و کارشناسان خرید محصولات کشاورزی | مکانیک‌ها و تکنسین‌های تعمیر ادوات کشاورزی | پیمانکاران نیروی کار کشاورزی | کارگران مزارع، پرورش گل و گیاه و گلخانه‌ها | کارگران دامداری، مرغداری و پرورش آبزیان | سرپرستان رده‌اول کارکنان کشاورزی، شیلات و جنگل‌داری | دانشمندان و متخصصان صنایع غذایی | تکنسین‌های جنگل‌داری و حفاظت از منابع طبیعی | مدیران تولید صنعتی | تکنسین‌های کشاورزی دقیق | کارشناسان و ارزیابان مراتع | متخصصان علوم خاک و گیاه‌پزشکی</t>
+          <t>مهندسان کشاورزی | بازرسان محصولات و فرآورده‌های کشاورزی | استادان و مدرسان علوم کشاورزی در دانشگاه‌ها و مراکز آموزش عالی | تکنسین‌های کشاورزی | تکنسین‌ها و کارشناسان اصلاح نژاد و پرورش دام | متخصصان علوم دامی | تکنسین‌های فراوری سوخت‌های زیستی | مدیران تولید سوخت‌های زیستی | خریداران و کارشناسان خرید محصولات کشاورزی | مکانیک و تکنسین خدمات ماشین‌آلات کشاورزی | پیمانکاران و تأمین‌کنندگان نیروی کار کشاورزی | کارگران زراعت، نهالستان و گلخانه | کارگران پرورش دام، طیور و آبزیان | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | متخصصان و کارشناسان علوم و صنایع غذایی | کاردان‌ها و تکنسین‌های جنگل‌داری و حفاظت منابع طبیعی | مدیران تولید صنعتی | تکنسین‌های کشاورزی دقیق | مدیران و کارشناسان مدیریت مراتع | متخصصان خاک‌شناسی و علوم گیاهی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | درک مطلب | سخن گفتن | یادگیری فعال | نظارت | نگارش | ریاضیات | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | سخن گفتن | یادگیری فعال | نظارت | نگارش | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ساختمان و سازه | مدیریت و امور اداری | ریاضیات | مهندسی و فناوری | خدمات مشتریان و خدمات فردی | مکانیک | تولید و فرآوری | اقتصاد و حسابداری | ایمنی و امنیت عمومی | پرسنلی و منابع انسانی | طراحی | زبان انگلیسی | اداری | رایانه و الکترونیک | آموزش و تدریس | حقوق و مقررات دولتی | بازاریابی و فروش</t>
+          <t>ساختمان و ساخت‌وساز | مدیریت و اداره | ریاضیات | مهندسی و فناوری | خدمات مشتری و شخصی | مکانیک | تولید و فرآوری | اقتصاد و حسابداری | ایمنی و امنیت عمومی | پرسنل و منابع انسانی | طراحی | زبان انگلیسی | اداری | رایانه و الکترونیک | آموزش و پرورش | قانون و دولت | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | مرتب‌سازی اطلاعات | بیان کتبی | استدلال استقرایی | تجسم فضایی | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری طبقه‌بندی | دید دور | انعطاف‌پذیری بستن ذهنی | استدلال ریاضی | روانی ایده‌ها | توجه انتخابی | تسهیلات محاسباتی | سرعت بستن ذهنی | ابتکار و اصالت | تمایز رنگ‌ها | تسهیم زمان | سرعت ادراک</t>
+          <t>حساسیت به مسئله | درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | ترتیب‌دهی اطلاعات | بیان کتبی | استدلال استقرایی | تجسم | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | بینایی دور | انعطاف‌پذیری بستار | استدلال ریاضی | روانی ایده‌ها | توجه انتخابی | توانایی عددی | سرعت بستار | اصالت | تشخیص رنگ بصری | تقسیم توجه | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مهندسان معمار، به‌جز معماران منظر و سازه‌های دریایی | مدیران پروژه‌های معماری و مهندسی | تکنسین‌ها و کاردان‌های مهندسی عمران | مهندسان عمران | بازرسان ساختمان و سازه | مترورها و برآوردکنندگان هزینه | مدیران تاسیسات و اماکن | سرپرستان رده‌اول کارگران ساختمانی و عملیات استخراج | سرپرستان رده‌اول محوطه‌سازی، فضای سبز و باغبانی | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | مدیران عامل و مدیران عملیاتی | مدیران تولید زمین‌گرمایی | بازرسان و کارشناسان املاک دولتی | مهندسان صنایع | مدیران تولید صنعتی | کارگران نگهداری و تعمیرات عمومی | مهندسان مکانیک | کارشناسان مدیریت پروژه | مدیران نصب تاسیسات انرژی خورشیدی | مدیران توسعه پروژه‌های انرژی بادی</t>
+          <t>مهندسان معمار، به‌جز معماران منظر و سازه‌های دریایی | مدیران فنی و مهندسی و معماری | کارشناسان و تکنسین‌های مهندسی عمران | مهندسان عمران | بازرسان ساخت‌وساز و ساختمان | کارشناسان برآورد هزینه و مترورها | مدیران امور ساختمان و تأسیسات | سرپرستان رده‌اول مشاغل ساختمانی، عمرانی و استخراج | سرپرستان رده اول کارگران باغبانی، فضای سبز و نگهداری محوطه | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | مدیران کل و مدیران عملیات | مدیران تولید انرژی زمین‌گرمایی | بازرسان و ممیزان اموال دولتی | مهندسان صنایع | مدیران تولید صنعتی | کارگران عمومی تعمیرات و نگهداری تاسیسات | مهندسان مکانیک | کارشناسان مدیریت پروژه | مدیران اجرای پروژه‌های انرژی خورشیدی | مدیران توسعه پروژه‌های انرژی بادی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
